--- a/reports/ProdDetails/auditoria_motores_2026.xlsx
+++ b/reports/ProdDetails/auditoria_motores_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M436"/>
+  <dimension ref="A1:Q436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,26 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>mase_2026_prophet</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mase_2026_deepar</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mase_2026_ensemble</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mase_2026_stacking</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>smape_real_2026_ganador</t>
         </is>
       </c>
@@ -545,6 +565,18 @@
         <v>61.24013403017567</v>
       </c>
       <c r="M2" t="n">
+        <v>0.4963063237634774</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.450095876528359</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7949430319700936</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5194348901445333</v>
+      </c>
+      <c r="Q2" t="n">
         <v>48.66961268312976</v>
       </c>
     </row>
@@ -598,6 +630,18 @@
         <v>93.26206878076644</v>
       </c>
       <c r="M3" t="n">
+        <v>0.8262311900332535</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.098646869774287</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8267391176885887</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.7836170890646232</v>
+      </c>
+      <c r="Q3" t="n">
         <v>86.57333032599385</v>
       </c>
     </row>
@@ -651,6 +695,18 @@
         <v>173.1600803694304</v>
       </c>
       <c r="M4" t="n">
+        <v>2.365582653148682</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.166501179770702</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.547648273691073</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.820132518290808</v>
+      </c>
+      <c r="Q4" t="n">
         <v>104.66055648811</v>
       </c>
     </row>
@@ -704,6 +760,18 @@
         <v>200</v>
       </c>
       <c r="M5" t="n">
+        <v>1.015120880466472</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.06389338348019</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9913651049584395</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.071895424836601</v>
+      </c>
+      <c r="Q5" t="n">
         <v>127.6510638872723</v>
       </c>
     </row>
@@ -757,6 +825,18 @@
         <v>176.496443809585</v>
       </c>
       <c r="M6" t="n">
+        <v>0.5803795463807413</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5883138691891815</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5941469204063882</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.7339587226897314</v>
+      </c>
+      <c r="Q6" t="n">
         <v>102.9875115341954</v>
       </c>
     </row>
@@ -810,6 +890,18 @@
         <v>195.2761973908773</v>
       </c>
       <c r="M7" t="n">
+        <v>0.4183406213301439</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3919568923024921</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4070735629555424</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4471111978880775</v>
+      </c>
+      <c r="Q7" t="n">
         <v>131.9348246060965</v>
       </c>
     </row>
@@ -863,6 +955,18 @@
         <v>94.21368911118574</v>
       </c>
       <c r="M8" t="n">
+        <v>0.5174844501506475</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5963358296032216</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5463142300019932</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5160265082650543</v>
+      </c>
+      <c r="Q8" t="n">
         <v>85.58040308470515</v>
       </c>
     </row>
@@ -916,6 +1020,18 @@
         <v>165.7279429344774</v>
       </c>
       <c r="M9" t="n">
+        <v>0.4285685770245085</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.390460417547038</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5821509511025665</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.5685359880590555</v>
+      </c>
+      <c r="Q9" t="n">
         <v>90.12673306112453</v>
       </c>
     </row>
@@ -957,6 +1073,10 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -996,6 +1116,10 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1035,6 +1159,10 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1074,6 +1202,10 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1113,6 +1245,10 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1152,6 +1288,10 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1191,6 +1331,10 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1230,6 +1374,10 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1269,6 +1417,10 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1308,6 +1460,10 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1347,6 +1503,10 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1386,6 +1546,10 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1425,6 +1589,10 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1464,6 +1632,10 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1503,6 +1675,10 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1542,6 +1718,10 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1581,6 +1761,10 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1620,6 +1804,10 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1659,6 +1847,10 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1698,6 +1890,10 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1737,6 +1933,10 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1776,6 +1976,10 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1815,6 +2019,10 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1854,6 +2062,10 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1893,6 +2105,10 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1932,6 +2148,10 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1971,6 +2191,10 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2010,6 +2234,10 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2049,6 +2277,10 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2088,6 +2320,10 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2127,6 +2363,10 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2166,6 +2406,10 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2205,6 +2449,10 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2244,6 +2492,10 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2283,6 +2535,10 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2322,6 +2578,10 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2361,6 +2621,10 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2400,6 +2664,10 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2439,6 +2707,10 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2478,6 +2750,10 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2517,6 +2793,10 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2556,6 +2836,10 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2595,6 +2879,10 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2634,6 +2922,10 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2673,6 +2965,10 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2712,6 +3008,10 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2751,6 +3051,10 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2790,6 +3094,10 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2829,6 +3137,10 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2868,6 +3180,10 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2907,6 +3223,10 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2946,6 +3266,10 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2985,6 +3309,10 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3024,6 +3352,10 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3063,6 +3395,10 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3102,6 +3438,10 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3141,6 +3481,10 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3180,6 +3524,10 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3219,6 +3567,10 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3258,6 +3610,10 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3297,6 +3653,10 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3336,6 +3696,10 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3375,6 +3739,10 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3414,6 +3782,10 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3453,6 +3825,10 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3492,6 +3868,10 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3531,6 +3911,10 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3570,6 +3954,10 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3609,6 +3997,10 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3648,6 +4040,10 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3699,6 +4095,18 @@
         <v>39.97478212439506</v>
       </c>
       <c r="M80" t="n">
+        <v>0.4555062841808764</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.4069713013220761</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.5085883540940652</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.5058173249316193</v>
+      </c>
+      <c r="Q80" t="n">
         <v>33.87995079939812</v>
       </c>
     </row>
@@ -3752,6 +4160,18 @@
         <v>49.89123702160717</v>
       </c>
       <c r="M81" t="n">
+        <v>0.3030451127864988</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.2872670514909488</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.585877244264529</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.2936515032269564</v>
+      </c>
+      <c r="Q81" t="n">
         <v>49.08430182911074</v>
       </c>
     </row>
@@ -3805,6 +4225,18 @@
         <v>35.78272886699257</v>
       </c>
       <c r="M82" t="n">
+        <v>0.8137755510340209</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.5343411489681719</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.4165780295620921</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.4103593029175839</v>
+      </c>
+      <c r="Q82" t="n">
         <v>35.70451769743996</v>
       </c>
     </row>
@@ -3858,6 +4290,18 @@
         <v>28.48705255072218</v>
       </c>
       <c r="M83" t="n">
+        <v>1.179667993605369</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1.103867813246465</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2.74793967148028</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1.473530839096596</v>
+      </c>
+      <c r="Q83" t="n">
         <v>24.46299231047144</v>
       </c>
     </row>
@@ -3911,6 +4355,18 @@
         <v>45.80250055257215</v>
       </c>
       <c r="M84" t="n">
+        <v>0.6271345788484938</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.5266508422664926</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.079926264352235</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.922135717319488</v>
+      </c>
+      <c r="Q84" t="n">
         <v>36.01738603043891</v>
       </c>
     </row>
@@ -3964,6 +4420,18 @@
         <v>16.70705585728497</v>
       </c>
       <c r="M85" t="n">
+        <v>2.058573381107975</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.3630798109612255</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2.488209404531707</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.5312853560638173</v>
+      </c>
+      <c r="Q85" t="n">
         <v>10.88932529428756</v>
       </c>
     </row>
@@ -4017,6 +4485,18 @@
         <v>40.53502607348377</v>
       </c>
       <c r="M86" t="n">
+        <v>0.4205761519324955</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.2498288259704159</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.3697586430001045</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.3137800114156912</v>
+      </c>
+      <c r="Q86" t="n">
         <v>32.00917839613845</v>
       </c>
     </row>
@@ -4070,6 +4550,18 @@
         <v>25.82610549186775</v>
       </c>
       <c r="M87" t="n">
+        <v>0.6702829229601271</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.2276596253734401</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.8583224315618208</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.2067000598622112</v>
+      </c>
+      <c r="Q87" t="n">
         <v>25.36608197142204</v>
       </c>
     </row>
@@ -4123,6 +4615,18 @@
         <v>37.52746293871189</v>
       </c>
       <c r="M88" t="n">
+        <v>4.457174721524174</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1.204169251209761</v>
+      </c>
+      <c r="O88" t="n">
+        <v>2.539095539489514</v>
+      </c>
+      <c r="P88" t="n">
+        <v>2.14706447642067</v>
+      </c>
+      <c r="Q88" t="n">
         <v>19.3893123550352</v>
       </c>
     </row>
@@ -4176,6 +4680,18 @@
         <v>35.69559401894602</v>
       </c>
       <c r="M89" t="n">
+        <v>0.9974248941307398</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.3768503411550771</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1.097773144977661</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.5120596922899732</v>
+      </c>
+      <c r="Q89" t="n">
         <v>26.95554351334863</v>
       </c>
     </row>
@@ -4229,6 +4745,18 @@
         <v>52.77333623010384</v>
       </c>
       <c r="M90" t="n">
+        <v>1.294630427101239</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.5926805638344482</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.7045956303950589</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.76517636881665</v>
+      </c>
+      <c r="Q90" t="n">
         <v>40.21407848952187</v>
       </c>
     </row>
@@ -4282,6 +4810,18 @@
         <v>38.72389555404084</v>
       </c>
       <c r="M91" t="n">
+        <v>0.4342322323875626</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.2982502142127217</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.6793948045221307</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.3172357378678375</v>
+      </c>
+      <c r="Q91" t="n">
         <v>36.96881575245713</v>
       </c>
     </row>
@@ -4335,6 +4875,18 @@
         <v>68.80207437701398</v>
       </c>
       <c r="M92" t="n">
+        <v>1.877691002817825</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.681641805888758</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1.115538434160179</v>
+      </c>
+      <c r="P92" t="n">
+        <v>3.112774773853696</v>
+      </c>
+      <c r="Q92" t="n">
         <v>23.00892757281023</v>
       </c>
     </row>
@@ -4388,6 +4940,18 @@
         <v>90.06167454730412</v>
       </c>
       <c r="M93" t="n">
+        <v>0.6756017249798953</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.5732490190358708</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.9104594819024158</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1.763405119966019</v>
+      </c>
+      <c r="Q93" t="n">
         <v>53.6087624436134</v>
       </c>
     </row>
@@ -4441,6 +5005,18 @@
         <v>66.50970651659432</v>
       </c>
       <c r="M94" t="n">
+        <v>0.6713894235158405</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.4640343863973677</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.9543056628382035</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.02458144853286</v>
+      </c>
+      <c r="Q94" t="n">
         <v>44.48013440580276</v>
       </c>
     </row>
@@ -4494,6 +5070,18 @@
         <v>45.97427845925774</v>
       </c>
       <c r="M95" t="n">
+        <v>0.5902591895201902</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.4156612232665267</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.8704380706595651</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.5040641079750157</v>
+      </c>
+      <c r="Q95" t="n">
         <v>38.56333576686337</v>
       </c>
     </row>
@@ -4547,6 +5135,18 @@
         <v>31.00100721756643</v>
       </c>
       <c r="M96" t="n">
+        <v>1.244725940054027</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.9846471115568927</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1.971135556509645</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1.583042708105755</v>
+      </c>
+      <c r="Q96" t="n">
         <v>21.48800699001515</v>
       </c>
     </row>
@@ -4600,6 +5200,18 @@
         <v>43.57830819020272</v>
       </c>
       <c r="M97" t="n">
+        <v>0.4430007219886728</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.4716153748538619</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.8338278336844157</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.6817373154385162</v>
+      </c>
+      <c r="Q97" t="n">
         <v>35.79000552993054</v>
       </c>
     </row>
@@ -4653,6 +5265,18 @@
         <v>42.05150021085679</v>
       </c>
       <c r="M98" t="n">
+        <v>0.5006153304011669</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.4968281777811151</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.5587473843538482</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.4711902932129412</v>
+      </c>
+      <c r="Q98" t="n">
         <v>41.29042410555367</v>
       </c>
     </row>
@@ -4706,6 +5330,18 @@
         <v>39.86478996571643</v>
       </c>
       <c r="M99" t="n">
+        <v>0.7815048609623633</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.5562538994453331</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1.089527323520796</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.47344136408403</v>
+      </c>
+      <c r="Q99" t="n">
         <v>39.08021611955975</v>
       </c>
     </row>
@@ -4759,6 +5395,18 @@
         <v>52.31088968852596</v>
       </c>
       <c r="M100" t="n">
+        <v>0.566793001255937</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.4151038163988781</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.6738413089322512</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.6035945514036738</v>
+      </c>
+      <c r="Q100" t="n">
         <v>33.37967588740923</v>
       </c>
     </row>
@@ -4812,6 +5460,18 @@
         <v>88.81313273437927</v>
       </c>
       <c r="M101" t="n">
+        <v>0.4742380589615448</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.4832699919358471</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.8928030343952438</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1.552826190815091</v>
+      </c>
+      <c r="Q101" t="n">
         <v>42.9492735258218</v>
       </c>
     </row>
@@ -4865,6 +5525,18 @@
         <v>81.14443555407458</v>
       </c>
       <c r="M102" t="n">
+        <v>0.4690224094922275</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.53167831980122</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1.109470759669082</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1.418822426832713</v>
+      </c>
+      <c r="Q102" t="n">
         <v>44.78064191913121</v>
       </c>
     </row>
@@ -4918,6 +5590,18 @@
         <v>18.6235669014579</v>
       </c>
       <c r="M103" t="n">
+        <v>1.61493727449601</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.5594828489604892</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.5619296877662241</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.6066098370660914</v>
+      </c>
+      <c r="Q103" t="n">
         <v>17.5359268672315</v>
       </c>
     </row>
@@ -4971,6 +5655,18 @@
         <v>33.10834761447673</v>
       </c>
       <c r="M104" t="n">
+        <v>0.9345143620044524</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.7019696760689599</v>
+      </c>
+      <c r="O104" t="n">
+        <v>3.291262910385249</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1.05530525175576</v>
+      </c>
+      <c r="Q104" t="n">
         <v>18.76511246705537</v>
       </c>
     </row>
@@ -5024,6 +5720,18 @@
         <v>14.02831735042523</v>
       </c>
       <c r="M105" t="n">
+        <v>3.220485298679879</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.7787907270095761</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.9324120350946704</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.9502312140316849</v>
+      </c>
+      <c r="Q105" t="n">
         <v>10.70639300274082</v>
       </c>
     </row>
@@ -5077,6 +5785,18 @@
         <v>52.05167679211357</v>
       </c>
       <c r="M106" t="n">
+        <v>0.4788721253382748</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.2384633928367697</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1.145584417407361</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.7029514278505737</v>
+      </c>
+      <c r="Q106" t="n">
         <v>20.28023724444433</v>
       </c>
     </row>
@@ -5130,6 +5850,18 @@
         <v>42.04194505145672</v>
       </c>
       <c r="M107" t="n">
+        <v>1.998037412628928</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.9560202085548268</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1.450919149641713</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1.177730672746406</v>
+      </c>
+      <c r="Q107" t="n">
         <v>32.9432662917778</v>
       </c>
     </row>
@@ -5183,6 +5915,18 @@
         <v>46.97724146338898</v>
       </c>
       <c r="M108" t="n">
+        <v>0.6026021501914848</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.4495408051153559</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.6488927335030148</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.5347114012897224</v>
+      </c>
+      <c r="Q108" t="n">
         <v>41.35723534707326</v>
       </c>
     </row>
@@ -5236,6 +5980,18 @@
         <v>55.57317513170248</v>
       </c>
       <c r="M109" t="n">
+        <v>0.6055061973233477</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.3441939256586498</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.5499252298002286</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.4603796036589775</v>
+      </c>
+      <c r="Q109" t="n">
         <v>39.83285303054647</v>
       </c>
     </row>
@@ -5289,6 +6045,18 @@
         <v>33.82717036410313</v>
       </c>
       <c r="M110" t="n">
+        <v>0.8942252792237247</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1.026926094062717</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.9500611222152866</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1.317499702774305</v>
+      </c>
+      <c r="Q110" t="n">
         <v>26.46793375056999</v>
       </c>
     </row>
@@ -5342,6 +6110,18 @@
         <v>29.04926637734889</v>
       </c>
       <c r="M111" t="n">
+        <v>2.426674840354688</v>
+      </c>
+      <c r="N111" t="n">
+        <v>1.012911610849261</v>
+      </c>
+      <c r="O111" t="n">
+        <v>3.059875601757068</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1.413004264588021</v>
+      </c>
+      <c r="Q111" t="n">
         <v>19.42546521848106</v>
       </c>
     </row>
@@ -5395,6 +6175,18 @@
         <v>62.09329308948924</v>
       </c>
       <c r="M112" t="n">
+        <v>1.238903092535918</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.8783839590588748</v>
+      </c>
+      <c r="O112" t="n">
+        <v>2.009362178039313</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1.138171982381162</v>
+      </c>
+      <c r="Q112" t="n">
         <v>40.5328700927482</v>
       </c>
     </row>
@@ -5448,6 +6240,18 @@
         <v>30.66955902514507</v>
       </c>
       <c r="M113" t="n">
+        <v>0.9365177259437168</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.7185815243583884</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1.913339057964351</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.8644793359324916</v>
+      </c>
+      <c r="Q113" t="n">
         <v>26.32796374983769</v>
       </c>
     </row>
@@ -5501,6 +6305,18 @@
         <v>47.00853901948749</v>
       </c>
       <c r="M114" t="n">
+        <v>1.126544974972913</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.8921019091385568</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.931726308383957</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1.577317810641582</v>
+      </c>
+      <c r="Q114" t="n">
         <v>27.98990702756037</v>
       </c>
     </row>
@@ -5554,6 +6370,18 @@
         <v>62.35194596018177</v>
       </c>
       <c r="M115" t="n">
+        <v>0.3858774520831448</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.3761900954715849</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.3704101198634256</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.7294115393287948</v>
+      </c>
+      <c r="Q115" t="n">
         <v>40.23208629920414</v>
       </c>
     </row>
@@ -5607,6 +6435,18 @@
         <v>44.08754531026054</v>
       </c>
       <c r="M116" t="n">
+        <v>0.5376590005803517</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.3226948179497845</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.4322926569799316</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.4859370965897064</v>
+      </c>
+      <c r="Q116" t="n">
         <v>32.27411002311214</v>
       </c>
     </row>
@@ -5660,6 +6500,18 @@
         <v>37.26133020369928</v>
       </c>
       <c r="M117" t="n">
+        <v>0.3212996928578917</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.2315146158362704</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3111592564047541</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3090484857906119</v>
+      </c>
+      <c r="Q117" t="n">
         <v>29.66904886426572</v>
       </c>
     </row>
@@ -5713,6 +6565,18 @@
         <v>41.59629888150341</v>
       </c>
       <c r="M118" t="n">
+        <v>0.9140352196484824</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.7602723944857496</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.7293528802973596</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.7386445851180943</v>
+      </c>
+      <c r="Q118" t="n">
         <v>41.38868247093798</v>
       </c>
     </row>
@@ -5766,6 +6630,18 @@
         <v>38.80479933969608</v>
       </c>
       <c r="M119" t="n">
+        <v>1.440928608784042</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6575464449598778</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1.291504441001166</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.7182507902512901</v>
+      </c>
+      <c r="Q119" t="n">
         <v>37.4840093545261</v>
       </c>
     </row>
@@ -5819,6 +6695,18 @@
         <v>22.01949888309036</v>
       </c>
       <c r="M120" t="n">
+        <v>3.010459533714581</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.6269332649536267</v>
+      </c>
+      <c r="O120" t="n">
+        <v>2.306223096808929</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1.130009214149456</v>
+      </c>
+      <c r="Q120" t="n">
         <v>12.29969241521232</v>
       </c>
     </row>
@@ -5872,6 +6760,18 @@
         <v>35.89750564092897</v>
       </c>
       <c r="M121" t="n">
+        <v>1.035506170664395</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.4818859148061782</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.5265381449950961</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.5792185790395007</v>
+      </c>
+      <c r="Q121" t="n">
         <v>31.06198190433289</v>
       </c>
     </row>
@@ -5913,6 +6813,10 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5952,6 +6856,10 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5991,6 +6899,10 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6030,6 +6942,10 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6069,6 +6985,10 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6108,6 +7028,10 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6147,6 +7071,10 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6186,6 +7114,10 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6225,6 +7157,10 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6264,6 +7200,10 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6303,6 +7243,10 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6342,6 +7286,10 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6393,6 +7341,18 @@
         <v>116.505225593667</v>
       </c>
       <c r="M134" t="n">
+        <v>0.4000284423645212</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4130192807256705</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.407817667211308</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3898955380369395</v>
+      </c>
+      <c r="Q134" t="n">
         <v>108.3514387296261</v>
       </c>
     </row>
@@ -6446,6 +7406,18 @@
         <v>52.04342177883449</v>
       </c>
       <c r="M135" t="n">
+        <v>0.2009687080225146</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.1468068830376548</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.2527720517563016</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.2514813858200861</v>
+      </c>
+      <c r="Q135" t="n">
         <v>38.43532723638933</v>
       </c>
     </row>
@@ -6499,6 +7471,18 @@
         <v>107.4196761888475</v>
       </c>
       <c r="M136" t="n">
+        <v>0.4613408919897806</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.439536364106311</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.4602492217469126</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.5490998676016643</v>
+      </c>
+      <c r="Q136" t="n">
         <v>78.40975782108053</v>
       </c>
     </row>
@@ -6552,6 +7536,18 @@
         <v>115.6732776948174</v>
       </c>
       <c r="M137" t="n">
+        <v>1.072560182627694</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.6465604464381248</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.7244082980623667</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.970990083678572</v>
+      </c>
+      <c r="Q137" t="n">
         <v>70.22626367256269</v>
       </c>
     </row>
@@ -6605,6 +7601,18 @@
         <v>133.5720711379641</v>
       </c>
       <c r="M138" t="n">
+        <v>0.3425858583654801</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.27962736133479</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.2253385655171356</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.5657824486385155</v>
+      </c>
+      <c r="Q138" t="n">
         <v>116.2289461400024</v>
       </c>
     </row>
@@ -6658,6 +7666,18 @@
         <v>67.12974373713892</v>
       </c>
       <c r="M139" t="n">
+        <v>0.2567089205464898</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.2415899168684736</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.395761651410367</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.2419133962464505</v>
+      </c>
+      <c r="Q139" t="n">
         <v>61.61565647244387</v>
       </c>
     </row>
@@ -6711,6 +7731,18 @@
         <v>180.4148606121412</v>
       </c>
       <c r="M140" t="n">
+        <v>0.5149822111509564</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.4577490786430586</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.4818739320850023</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.5139515261536609</v>
+      </c>
+      <c r="Q140" t="n">
         <v>134.9587600595286</v>
       </c>
     </row>
@@ -6764,6 +7796,18 @@
         <v>53.20913962367286</v>
       </c>
       <c r="M141" t="n">
+        <v>0.4814330046609544</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3930557962764996</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.7725147814135761</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.5480607426738789</v>
+      </c>
+      <c r="Q141" t="n">
         <v>38.31955910599674</v>
       </c>
     </row>
@@ -6817,6 +7861,18 @@
         <v>91.29548479560816</v>
       </c>
       <c r="M142" t="n">
+        <v>0.7127672635015216</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.7470180640544396</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.876852125722787</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.7760215396669538</v>
+      </c>
+      <c r="Q142" t="n">
         <v>79.56093018057274</v>
       </c>
     </row>
@@ -6870,6 +7926,18 @@
         <v>96.3277741330741</v>
       </c>
       <c r="M143" t="n">
+        <v>0.4380872724699952</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.4191572395597502</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3965124735829798</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.6391101501608156</v>
+      </c>
+      <c r="Q143" t="n">
         <v>74.42274779713486</v>
       </c>
     </row>
@@ -6923,6 +7991,18 @@
         <v>30.78245676548453</v>
       </c>
       <c r="M144" t="n">
+        <v>0.665654576058322</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.6338730709591652</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.7887869253719363</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.7211966837569646</v>
+      </c>
+      <c r="Q144" t="n">
         <v>27.55869664488046</v>
       </c>
     </row>
@@ -6976,6 +8056,18 @@
         <v>65.95879525747603</v>
       </c>
       <c r="M145" t="n">
+        <v>0.3036187876004591</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.2577020136716153</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0.2637616939252427</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.3438004266519655</v>
+      </c>
+      <c r="Q145" t="n">
         <v>57.1725834341672</v>
       </c>
     </row>
@@ -7029,6 +8121,18 @@
         <v>86.20456825856974</v>
       </c>
       <c r="M146" t="n">
+        <v>1.587089649448088</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1.593090259051785</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1.750079493345953</v>
+      </c>
+      <c r="P146" t="n">
+        <v>1.828340012289714</v>
+      </c>
+      <c r="Q146" t="n">
         <v>66.24399994166637</v>
       </c>
     </row>
@@ -7070,6 +8174,10 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7109,6 +8217,10 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7148,6 +8260,10 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7187,6 +8303,10 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7226,6 +8346,10 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7265,6 +8389,10 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7304,6 +8432,10 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7343,6 +8475,10 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7382,6 +8518,10 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7421,6 +8561,10 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7460,6 +8604,10 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7499,6 +8647,10 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7549,7 +8701,19 @@
       <c r="L159" t="n">
         <v>200</v>
       </c>
-      <c r="M159" t="inlineStr"/>
+      <c r="M159" t="n">
+        <v>1.105166055196482</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0.3870143609958089</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.5176933854106238</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.363905325443787</v>
+      </c>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7600,7 +8764,19 @@
       <c r="L160" t="n">
         <v>200</v>
       </c>
-      <c r="M160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>0.9057429241278901</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0.3581689274966536</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.6777613655333952</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.3580786026200873</v>
+      </c>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7651,7 +8827,19 @@
       <c r="L161" t="n">
         <v>200</v>
       </c>
-      <c r="M161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>0.7407403341626122</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0.1110723996228335</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.536624499251336</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0.1108108108108108</v>
+      </c>
+      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7702,7 +8890,19 @@
       <c r="L162" t="n">
         <v>199.6638387097672</v>
       </c>
-      <c r="M162" t="inlineStr"/>
+      <c r="M162" t="n">
+        <v>0.5184590273623254</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0.5602618510924585</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0.5561683081848757</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0.3725133668342273</v>
+      </c>
+      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7753,7 +8953,19 @@
       <c r="L163" t="n">
         <v>144.8279678835104</v>
       </c>
-      <c r="M163" t="inlineStr"/>
+      <c r="M163" t="n">
+        <v>0.2333534056604101</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0.2625068546952129</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.1773084597046224</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0.1926527842290186</v>
+      </c>
+      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7804,7 +9016,19 @@
       <c r="L164" t="n">
         <v>200</v>
       </c>
-      <c r="M164" t="inlineStr"/>
+      <c r="M164" t="n">
+        <v>1.224256014275574</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0.569444444445757</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0.8541666666666667</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7855,7 +9079,19 @@
       <c r="L165" t="n">
         <v>200</v>
       </c>
-      <c r="M165" t="inlineStr"/>
+      <c r="M165" t="n">
+        <v>0.820044667391302</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0.2662337662372822</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.7987012987012986</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0.2662337662337662</v>
+      </c>
+      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7906,7 +9142,19 @@
       <c r="L166" t="n">
         <v>200</v>
       </c>
-      <c r="M166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>1.009091411913665</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0.4361702127679866</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0.4361702127659575</v>
+      </c>
+      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7957,7 +9205,19 @@
       <c r="L167" t="n">
         <v>200</v>
       </c>
-      <c r="M167" t="inlineStr"/>
+      <c r="M167" t="n">
+        <v>0.8681931305332128</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0.6959608358629999</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0.9203835367646895</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0.6628175519630485</v>
+      </c>
+      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8008,7 +9268,19 @@
       <c r="L168" t="n">
         <v>200</v>
       </c>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>0.4549874685369547</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0.4460024627640553</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0.8080721173059833</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0.3464788732394366</v>
+      </c>
+      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8059,7 +9331,19 @@
       <c r="L169" t="n">
         <v>200</v>
       </c>
-      <c r="M169" t="inlineStr"/>
+      <c r="M169" t="n">
+        <v>0.5433587301715964</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0.3844571295159459</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0.6517063821392561</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0.384375</v>
+      </c>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8110,7 +9394,19 @@
       <c r="L170" t="n">
         <v>200</v>
       </c>
-      <c r="M170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>0.5845976183130868</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0.5961118991257567</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0.6104012559298474</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0.5030674846625767</v>
+      </c>
+      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8161,7 +9457,19 @@
       <c r="L171" t="n">
         <v>200</v>
       </c>
-      <c r="M171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>0.3367573865803006</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0.3376751194637472</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.3285450647161058</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.3314424635332253</v>
+      </c>
+      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8213,6 +9521,18 @@
         <v>200</v>
       </c>
       <c r="M172" t="n">
+        <v>1.872250313302877</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1.707629424766975</v>
+      </c>
+      <c r="O172" t="n">
+        <v>1.726954005503625</v>
+      </c>
+      <c r="P172" t="n">
+        <v>1.952380952380952</v>
+      </c>
+      <c r="Q172" t="n">
         <v>147.8365405085683</v>
       </c>
     </row>
@@ -8266,6 +9586,18 @@
         <v>73.13160929707514</v>
       </c>
       <c r="M173" t="n">
+        <v>1.053616336228885</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1.269136572321394</v>
+      </c>
+      <c r="O173" t="n">
+        <v>1.041988070411697</v>
+      </c>
+      <c r="P173" t="n">
+        <v>1.017848528123216</v>
+      </c>
+      <c r="Q173" t="n">
         <v>73.11516905421215</v>
       </c>
     </row>
@@ -8318,7 +9650,19 @@
       <c r="L174" t="n">
         <v>200</v>
       </c>
-      <c r="M174" t="inlineStr"/>
+      <c r="M174" t="n">
+        <v>1.022276943142461</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0.8310801006766012</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.5011976171700316</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0.4900398406374502</v>
+      </c>
+      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8369,7 +9713,19 @@
       <c r="L175" t="n">
         <v>200</v>
       </c>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>0.67435859882881</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.4272156930902298</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0.6077205724611067</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0.3951807228915662</v>
+      </c>
+      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8420,7 +9776,19 @@
       <c r="L176" t="n">
         <v>200</v>
       </c>
-      <c r="M176" t="inlineStr"/>
+      <c r="M176" t="n">
+        <v>0.5702489689196267</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0.3952365096482866</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0.5556756612331436</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0.3951807228915662</v>
+      </c>
+      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8472,6 +9840,18 @@
         <v>200</v>
       </c>
       <c r="M177" t="n">
+        <v>0.4686778328157057</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0.5176062028985906</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0.3667041556103072</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0.5331599479843954</v>
+      </c>
+      <c r="Q177" t="n">
         <v>120.2066066659431</v>
       </c>
     </row>
@@ -8524,7 +9904,19 @@
       <c r="L178" t="n">
         <v>154.1318504294555</v>
       </c>
-      <c r="M178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>0.290757386448554</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0.3651510929589686</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0.2844894316872301</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0.2916158553652481</v>
+      </c>
+      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8575,7 +9967,19 @@
       <c r="L179" t="n">
         <v>200</v>
       </c>
-      <c r="M179" t="inlineStr"/>
+      <c r="M179" t="n">
+        <v>0.4356569760654588</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0.5909545365407932</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0.4811158593137472</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0.3356070941336971</v>
+      </c>
+      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8626,7 +10030,19 @@
       <c r="L180" t="n">
         <v>179.6461449692756</v>
       </c>
-      <c r="M180" t="inlineStr"/>
+      <c r="M180" t="n">
+        <v>0.2796546085828516</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0.160413560074882</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0.18477135285524</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0.157335218440349</v>
+      </c>
+      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8677,7 +10093,19 @@
       <c r="L181" t="n">
         <v>200</v>
       </c>
-      <c r="M181" t="inlineStr"/>
+      <c r="M181" t="n">
+        <v>0.3948553187655165</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0.3622748304315664</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0.4152703067514402</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0.3451178451178452</v>
+      </c>
+      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8728,7 +10156,19 @@
       <c r="L182" t="n">
         <v>191.024244508394</v>
       </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="n">
+        <v>0.3503685646891333</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0.2809649340768117</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0.2703776717989387</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0.2220213803842448</v>
+      </c>
+      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8779,7 +10219,19 @@
       <c r="L183" t="n">
         <v>179.9171418242176</v>
       </c>
-      <c r="M183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>1.187059407549927</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1.648989452497649</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0.6046151518269768</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0.531230090130983</v>
+      </c>
+      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8830,7 +10282,19 @@
       <c r="L184" t="n">
         <v>200</v>
       </c>
-      <c r="M184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>0.6437318693329118</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0.5327893131970481</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0.7089906758597163</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0.1469534050179211</v>
+      </c>
+      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8881,7 +10345,19 @@
       <c r="L185" t="n">
         <v>200</v>
       </c>
-      <c r="M185" t="inlineStr"/>
+      <c r="M185" t="n">
+        <v>0.2180191128138514</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0.6004416844136652</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0.3549191974518905</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0.09761904761904762</v>
+      </c>
+      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8932,7 +10408,19 @@
       <c r="L186" t="n">
         <v>200</v>
       </c>
-      <c r="M186" t="inlineStr"/>
+      <c r="M186" t="n">
+        <v>1.999242274259969</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0.3981850209302953</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0.8120120339070427</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0.2554517133956387</v>
+      </c>
+      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8981,7 +10469,19 @@
         <v>200</v>
       </c>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
+      <c r="M187" t="n">
+        <v>0.9654673327759061</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0.0007707145863874081</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0.8075951870712453</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9032,7 +10532,19 @@
       <c r="L188" t="n">
         <v>200</v>
       </c>
-      <c r="M188" t="inlineStr"/>
+      <c r="M188" t="n">
+        <v>1.738803635744444</v>
+      </c>
+      <c r="N188" t="n">
+        <v>1.233222938964107</v>
+      </c>
+      <c r="O188" t="n">
+        <v>1.467409756075955</v>
+      </c>
+      <c r="P188" t="n">
+        <v>1.233082706766917</v>
+      </c>
+      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9083,7 +10595,19 @@
       <c r="L189" t="n">
         <v>200</v>
       </c>
-      <c r="M189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>1.108957722649681</v>
+      </c>
+      <c r="N189" t="n">
+        <v>1.187423864639559</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0.9657247261204679</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0.7235294117647059</v>
+      </c>
+      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9134,7 +10658,19 @@
       <c r="L190" t="n">
         <v>200</v>
       </c>
-      <c r="M190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>0.8142988934237811</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0.5106367542690712</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0.640863157851207</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0.5103734439834025</v>
+      </c>
+      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9185,7 +10721,19 @@
       <c r="L191" t="n">
         <v>200</v>
       </c>
-      <c r="M191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>0.5850293586601734</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0.2399246484520255</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0.5244807471400592</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0.239766081871345</v>
+      </c>
+      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9236,7 +10784,19 @@
       <c r="L192" t="n">
         <v>128.8723569912344</v>
       </c>
-      <c r="M192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>0.5157164247678562</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0.5709746038377651</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0.8416710279989053</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0.5143251253688388</v>
+      </c>
+      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9287,7 +10847,19 @@
       <c r="L193" t="n">
         <v>200</v>
       </c>
-      <c r="M193" t="inlineStr"/>
+      <c r="M193" t="n">
+        <v>0.7556728748917975</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0.3348913630618685</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0.5865705137904152</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0.2914691943127962</v>
+      </c>
+      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9338,7 +10910,19 @@
       <c r="L194" t="n">
         <v>193.6117702297933</v>
       </c>
-      <c r="M194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>0.5461104018186372</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0.2547657009575675</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0.5192968248127996</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0.3113761481824373</v>
+      </c>
+      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9389,7 +10973,19 @@
       <c r="L195" t="n">
         <v>200</v>
       </c>
-      <c r="M195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>0.4459799899573196</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0.3507959678608523</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0.4607641558375096</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0.3985419198055893</v>
+      </c>
+      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9440,7 +11036,19 @@
       <c r="L196" t="n">
         <v>170.1883818763876</v>
       </c>
-      <c r="M196" t="inlineStr"/>
+      <c r="M196" t="n">
+        <v>0.5817557193288908</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0.6298221241345734</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0.5090791052786605</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0.3897030264333268</v>
+      </c>
+      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9491,7 +11099,19 @@
       <c r="L197" t="n">
         <v>200</v>
       </c>
-      <c r="M197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>0.3778950377856465</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0.2698337880976363</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0.4959613689355202</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0.1373534338358459</v>
+      </c>
+      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9542,7 +11162,19 @@
       <c r="L198" t="n">
         <v>200</v>
       </c>
-      <c r="M198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>0.3257142885698632</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0.2603344641197909</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0.3619137080566656</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0.2201342281879194</v>
+      </c>
+      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9593,7 +11225,19 @@
       <c r="L199" t="n">
         <v>116.1253709860975</v>
       </c>
-      <c r="M199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>0.3455524717701707</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0.2857263274526446</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0.4058815112134732</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0.370135489704519</v>
+      </c>
+      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9642,7 +11286,19 @@
         <v>200</v>
       </c>
       <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
+      <c r="M200" t="n">
+        <v>0.900270485167302</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0.0001560867075162033</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0.4312772135554212</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9691,7 +11347,19 @@
         <v>200</v>
       </c>
       <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
+      <c r="M201" t="n">
+        <v>0.4236161481122729</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0.0004158099990402657</v>
+      </c>
+      <c r="O201" t="n">
+        <v>1.114130434782609</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9740,7 +11408,19 @@
         <v>200</v>
       </c>
       <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
+      <c r="M202" t="n">
+        <v>0.5636062765918135</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0.0006046084360479</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0.6043922690927107</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9791,7 +11471,19 @@
       <c r="L203" t="n">
         <v>194.3579676064005</v>
       </c>
-      <c r="M203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>0.635801411132183</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0.6426049818494844</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0.610012119892848</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0.5053197088898613</v>
+      </c>
+      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9842,7 +11534,19 @@
       <c r="L204" t="n">
         <v>200</v>
       </c>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="n">
+        <v>0.4730623016287984</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0.2320359201775368</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0.3992730943553419</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0.1975903614457831</v>
+      </c>
+      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9893,7 +11597,19 @@
       <c r="L205" t="n">
         <v>200</v>
       </c>
-      <c r="M205" t="inlineStr"/>
+      <c r="M205" t="n">
+        <v>0.4580452519190736</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0.3336574144924673</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0.422127324491707</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0.2992700729927007</v>
+      </c>
+      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9944,7 +11660,19 @@
       <c r="L206" t="n">
         <v>200</v>
       </c>
-      <c r="M206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>1.487455856310134</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0.6241116106606304</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0.8257924244901845</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0.623574144486692</v>
+      </c>
+      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9995,7 +11723,19 @@
       <c r="L207" t="n">
         <v>200</v>
       </c>
-      <c r="M207" t="inlineStr"/>
+      <c r="M207" t="n">
+        <v>1.308298704109882</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0.2500966379577075</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0.5637611920774379</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10046,7 +11786,19 @@
       <c r="L208" t="n">
         <v>200</v>
       </c>
-      <c r="M208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>1.128590926151096</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0.4574383350671221</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0.6935805671716654</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0.4572490706319702</v>
+      </c>
+      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10086,6 +11838,10 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10125,6 +11881,10 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10164,6 +11924,10 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10203,6 +11967,10 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10242,6 +12010,10 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10293,6 +12065,18 @@
         <v>92.18231498003905</v>
       </c>
       <c r="M214" t="n">
+        <v>0.4222008832897886</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0.3771269849016644</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0.2539740801255618</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0.2823007722442362</v>
+      </c>
+      <c r="Q214" t="n">
         <v>85.7359652556908</v>
       </c>
     </row>
@@ -10346,6 +12130,18 @@
         <v>26.88740093332276</v>
       </c>
       <c r="M215" t="n">
+        <v>1.423570888357263</v>
+      </c>
+      <c r="N215" t="n">
+        <v>1.018347848903064</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0.6401358261127176</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0.7984516458300764</v>
+      </c>
+      <c r="Q215" t="n">
         <v>21.14973430925023</v>
       </c>
     </row>
@@ -10399,6 +12195,18 @@
         <v>52.13101310337495</v>
       </c>
       <c r="M216" t="n">
+        <v>0.5680098956259918</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0.571899099132321</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0.5366875676461303</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0.5623854396545815</v>
+      </c>
+      <c r="Q216" t="n">
         <v>47.94477730719775</v>
       </c>
     </row>
@@ -10452,6 +12260,18 @@
         <v>42.51747941492351</v>
       </c>
       <c r="M217" t="n">
+        <v>0.3878800342767658</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0.4507922967366726</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0.3660586086142265</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0.5234293795699173</v>
+      </c>
+      <c r="Q217" t="n">
         <v>34.87607521600063</v>
       </c>
     </row>
@@ -10505,6 +12325,18 @@
         <v>43.94876356979679</v>
       </c>
       <c r="M218" t="n">
+        <v>0.368770880035023</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0.4073356285539468</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0.4113639726867217</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0.5414379846905031</v>
+      </c>
+      <c r="Q218" t="n">
         <v>37.31612122044224</v>
       </c>
     </row>
@@ -10558,6 +12390,18 @@
         <v>49.34364809314675</v>
       </c>
       <c r="M219" t="n">
+        <v>0.2601422172601193</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0.7726546418505833</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0.2221064366094657</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0.4280094812405191</v>
+      </c>
+      <c r="Q219" t="n">
         <v>32.21333019457885</v>
       </c>
     </row>
@@ -10611,6 +12455,18 @@
         <v>41.16939249198489</v>
       </c>
       <c r="M220" t="n">
+        <v>1.746448689374225</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1.037176772395813</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0.9839890150674696</v>
+      </c>
+      <c r="P220" t="n">
+        <v>1.819332463931268</v>
+      </c>
+      <c r="Q220" t="n">
         <v>25.39277043684599</v>
       </c>
     </row>
@@ -10664,6 +12520,18 @@
         <v>43.15965255521568</v>
       </c>
       <c r="M221" t="n">
+        <v>0.3525092729856952</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0.4029745383073035</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0.3129075973102494</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0.4916431280960782</v>
+      </c>
+      <c r="Q221" t="n">
         <v>34.55584114245553</v>
       </c>
     </row>
@@ -10717,6 +12585,18 @@
         <v>54.21541579316597</v>
       </c>
       <c r="M222" t="n">
+        <v>0.6837892756422741</v>
+      </c>
+      <c r="N222" t="n">
+        <v>1.331720117643262</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0.4673210782574907</v>
+      </c>
+      <c r="P222" t="n">
+        <v>1.73132202057355</v>
+      </c>
+      <c r="Q222" t="n">
         <v>19.18912897473146</v>
       </c>
     </row>
@@ -10770,6 +12650,18 @@
         <v>27.22618490444381</v>
       </c>
       <c r="M223" t="n">
+        <v>0.9373350850447364</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0.7392311348491534</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0.5710601395446542</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0.7215954912144246</v>
+      </c>
+      <c r="Q223" t="n">
         <v>22.23686936541685</v>
       </c>
     </row>
@@ -10823,6 +12715,18 @@
         <v>62.89742035808638</v>
       </c>
       <c r="M224" t="n">
+        <v>0.5355161955162439</v>
+      </c>
+      <c r="N224" t="n">
+        <v>1.136770065966799</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0.4504707873993655</v>
+      </c>
+      <c r="P224" t="n">
+        <v>2.16708678326318</v>
+      </c>
+      <c r="Q224" t="n">
         <v>18.52191591023819</v>
       </c>
     </row>
@@ -10876,6 +12780,18 @@
         <v>77.42891053817729</v>
       </c>
       <c r="M225" t="n">
+        <v>0.4784010996325458</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0.736827953898585</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0.3597711050508184</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0.6204582573291609</v>
+      </c>
+      <c r="Q225" t="n">
         <v>60.13075172573379</v>
       </c>
     </row>
@@ -10928,7 +12844,19 @@
       <c r="L226" t="n">
         <v>172.3430996346919</v>
       </c>
-      <c r="M226" t="inlineStr"/>
+      <c r="M226" t="n">
+        <v>0.2266566444494</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0.2495606007164172</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0.2218065722811142</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0.1989585736911736</v>
+      </c>
+      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10979,7 +12907,19 @@
       <c r="L227" t="n">
         <v>200</v>
       </c>
-      <c r="M227" t="inlineStr"/>
+      <c r="M227" t="n">
+        <v>0.1348641642969674</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0.09929335627832639</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0.1351103415097832</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0.07596109309865678</v>
+      </c>
+      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11030,7 +12970,19 @@
       <c r="L228" t="n">
         <v>147.5191482609954</v>
       </c>
-      <c r="M228" t="inlineStr"/>
+      <c r="M228" t="n">
+        <v>0.1688334626438485</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0.1674981118819415</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0.1103206385264748</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0.1214659373082105</v>
+      </c>
+      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11081,7 +13033,19 @@
       <c r="L229" t="n">
         <v>200</v>
       </c>
-      <c r="M229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>0.3515502564064775</v>
+      </c>
+      <c r="N229" t="n">
+        <v>0.3645252609548939</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0.3253193118029004</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0.298906439854192</v>
+      </c>
+      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11133,6 +13097,18 @@
         <v>99.71465593726315</v>
       </c>
       <c r="M230" t="n">
+        <v>0.7874702699528107</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0.6592043355805054</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0.6767052928794085</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0.6423378046747985</v>
+      </c>
+      <c r="Q230" t="n">
         <v>95.64498518050245</v>
       </c>
     </row>
@@ -11185,7 +13161,19 @@
       <c r="L231" t="n">
         <v>200</v>
       </c>
-      <c r="M231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>0.2104056009847581</v>
+      </c>
+      <c r="N231" t="n">
+        <v>0.1851522951494717</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0.2870504588913982</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0.06793703396851697</v>
+      </c>
+      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11237,6 +13225,18 @@
         <v>142.5409684499064</v>
       </c>
       <c r="M232" t="n">
+        <v>0.6010407513789499</v>
+      </c>
+      <c r="N232" t="n">
+        <v>0.6467834573251244</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0.5959728130090381</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0.5824815754018148</v>
+      </c>
+      <c r="Q232" t="n">
         <v>137.6049361089571</v>
       </c>
     </row>
@@ -11290,6 +13290,18 @@
         <v>101.9983621304178</v>
       </c>
       <c r="M233" t="n">
+        <v>0.677650942396835</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0.8519469548444485</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0.6931491886779847</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0.7061600861400472</v>
+      </c>
+      <c r="Q233" t="n">
         <v>92.13173554848004</v>
       </c>
     </row>
@@ -11343,6 +13355,18 @@
         <v>41.32863127402286</v>
       </c>
       <c r="M234" t="n">
+        <v>0.8971363195644693</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1.032541469616783</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0.7529134551556573</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0.8002347733680697</v>
+      </c>
+      <c r="Q234" t="n">
         <v>38.18140457022947</v>
       </c>
     </row>
@@ -11396,6 +13420,18 @@
         <v>197.6089031788505</v>
       </c>
       <c r="M235" t="n">
+        <v>0.3944266102330715</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0.4397557113247624</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0.3843170454498929</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0.4578742818084384</v>
+      </c>
+      <c r="Q235" t="n">
         <v>130.207324487643</v>
       </c>
     </row>
@@ -11449,6 +13485,18 @@
         <v>99.51705894181961</v>
       </c>
       <c r="M236" t="n">
+        <v>0.3108982220124355</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0.2865656741689094</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0.3161374100822015</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0.5911074580087966</v>
+      </c>
+      <c r="Q236" t="n">
         <v>77.64844161217391</v>
       </c>
     </row>
@@ -11501,7 +13549,19 @@
       <c r="L237" t="n">
         <v>200</v>
       </c>
-      <c r="M237" t="inlineStr"/>
+      <c r="M237" t="n">
+        <v>0.5459700897427122</v>
+      </c>
+      <c r="N237" t="n">
+        <v>0.5382642644875049</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0.5629419963343028</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0.4893899204244032</v>
+      </c>
+      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11552,7 +13612,19 @@
       <c r="L238" t="n">
         <v>200</v>
       </c>
-      <c r="M238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>0.8363694516032242</v>
+      </c>
+      <c r="N238" t="n">
+        <v>0.1898615749663894</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0.2214063498771642</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0.1575408261287224</v>
+      </c>
+      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11603,7 +13675,19 @@
       <c r="L239" t="n">
         <v>184.8073958566535</v>
       </c>
-      <c r="M239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>0.3126221895501518</v>
+      </c>
+      <c r="N239" t="n">
+        <v>0.3780791682205634</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0.2623481199487472</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0.2346889277227377</v>
+      </c>
+      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11655,6 +13739,18 @@
         <v>88.39889008593117</v>
       </c>
       <c r="M240" t="n">
+        <v>0.4339472940911706</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0.4090399288811854</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0.4394946740093981</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0.433370183147261</v>
+      </c>
+      <c r="Q240" t="n">
         <v>86.96839061044449</v>
       </c>
     </row>
@@ -11708,6 +13804,18 @@
         <v>95.721311933295</v>
       </c>
       <c r="M241" t="n">
+        <v>0.3641822034596468</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0.4239753500573046</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0.3514101421018029</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0.3238435746813323</v>
+      </c>
+      <c r="Q241" t="n">
         <v>87.82533318665149</v>
       </c>
     </row>
@@ -11761,6 +13869,18 @@
         <v>63.41516111385135</v>
       </c>
       <c r="M242" t="n">
+        <v>0.9401781360754821</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0.9774116363619297</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0.7025028162508269</v>
+      </c>
+      <c r="P242" t="n">
+        <v>1.339831700944567</v>
+      </c>
+      <c r="Q242" t="n">
         <v>38.67419069536405</v>
       </c>
     </row>
@@ -11814,6 +13934,18 @@
         <v>53.38786931400481</v>
       </c>
       <c r="M243" t="n">
+        <v>0.1832727036408004</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0.2602239846884933</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0.1591020589148894</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0.1792340563458112</v>
+      </c>
+      <c r="Q243" t="n">
         <v>51.53793469571896</v>
       </c>
     </row>
@@ -11866,7 +13998,19 @@
       <c r="L244" t="n">
         <v>153.6743352162732</v>
       </c>
-      <c r="M244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>0.5296083174058374</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0.6630227448145699</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0.6975633005882612</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0.42948308608267</v>
+      </c>
+      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11917,7 +14061,19 @@
       <c r="L245" t="n">
         <v>200</v>
       </c>
-      <c r="M245" t="inlineStr"/>
+      <c r="M245" t="n">
+        <v>0.5081626251965888</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0.4944087360504306</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0.6658985446403374</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0.2363112391930836</v>
+      </c>
+      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11968,7 +14124,19 @@
       <c r="L246" t="n">
         <v>198.9299007546998</v>
       </c>
-      <c r="M246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>0.3863343279920824</v>
+      </c>
+      <c r="N246" t="n">
+        <v>0.3953605260083382</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0.4152329551510137</v>
+      </c>
+      <c r="P246" t="n">
+        <v>0.1945542230272431</v>
+      </c>
+      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12019,7 +14187,19 @@
       <c r="L247" t="n">
         <v>200</v>
       </c>
-      <c r="M247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>1.069921718670129</v>
+      </c>
+      <c r="N247" t="n">
+        <v>0.5851995128033336</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0.4949662070337139</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0.3861852433281004</v>
+      </c>
+      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12070,7 +14250,19 @@
       <c r="L248" t="n">
         <v>200</v>
       </c>
-      <c r="M248" t="inlineStr"/>
+      <c r="M248" t="n">
+        <v>0.5538680273456871</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0.2709464950242204</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0.3966566130335826</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0.2884422110552763</v>
+      </c>
+      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12122,6 +14314,18 @@
         <v>168.1792165925686</v>
       </c>
       <c r="M249" t="n">
+        <v>0.5918479084654411</v>
+      </c>
+      <c r="N249" t="n">
+        <v>1.102507941948769</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0.722841775952255</v>
+      </c>
+      <c r="P249" t="n">
+        <v>1.158166425810214</v>
+      </c>
+      <c r="Q249" t="n">
         <v>59.32749050886825</v>
       </c>
     </row>
@@ -12175,6 +14379,18 @@
         <v>200</v>
       </c>
       <c r="M250" t="n">
+        <v>0.7527043563946426</v>
+      </c>
+      <c r="N250" t="n">
+        <v>0.8336819610745871</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0.8184045855546765</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0.7345276872964168</v>
+      </c>
+      <c r="Q250" t="n">
         <v>148.0428502678959</v>
       </c>
     </row>
@@ -12228,6 +14444,18 @@
         <v>73.03353347805752</v>
       </c>
       <c r="M251" t="n">
+        <v>0.3183103207308607</v>
+      </c>
+      <c r="N251" t="n">
+        <v>0.3975214393386352</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0.3536190837008889</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0.3354690727599436</v>
+      </c>
+      <c r="Q251" t="n">
         <v>62.78047231586389</v>
       </c>
     </row>
@@ -12281,6 +14509,18 @@
         <v>57.19568806431219</v>
       </c>
       <c r="M252" t="n">
+        <v>0.400940980167693</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0.6093717302209793</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0.7948988946575347</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0.4361884264424371</v>
+      </c>
+      <c r="Q252" t="n">
         <v>54.75586037349734</v>
       </c>
     </row>
@@ -12334,6 +14574,18 @@
         <v>89.91131763973604</v>
       </c>
       <c r="M253" t="n">
+        <v>0.339914271448541</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0.5601583986650476</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0.4233876437100231</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0.3156692597113919</v>
+      </c>
+      <c r="Q253" t="n">
         <v>85.00289404710729</v>
       </c>
     </row>
@@ -12387,6 +14639,18 @@
         <v>182.1238085303876</v>
       </c>
       <c r="M254" t="n">
+        <v>0.4658745918497241</v>
+      </c>
+      <c r="N254" t="n">
+        <v>0.5923615738677761</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0.4656774594194955</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0.5399776849153147</v>
+      </c>
+      <c r="Q254" t="n">
         <v>107.2880143122471</v>
       </c>
     </row>
@@ -12440,6 +14704,18 @@
         <v>153.2283549870294</v>
       </c>
       <c r="M255" t="n">
+        <v>0.4728598883853059</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0.7291350767299341</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0.4684091872876284</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0.427022863870927</v>
+      </c>
+      <c r="Q255" t="n">
         <v>132.9788825504028</v>
       </c>
     </row>
@@ -12493,6 +14769,18 @@
         <v>193.1941087796822</v>
       </c>
       <c r="M256" t="n">
+        <v>0.9971488533282604</v>
+      </c>
+      <c r="N256" t="n">
+        <v>1.138156578140991</v>
+      </c>
+      <c r="O256" t="n">
+        <v>1.144036528921518</v>
+      </c>
+      <c r="P256" t="n">
+        <v>1.254229530277282</v>
+      </c>
+      <c r="Q256" t="n">
         <v>115.2422247608137</v>
       </c>
     </row>
@@ -12546,6 +14834,18 @@
         <v>95.93678353256414</v>
       </c>
       <c r="M257" t="n">
+        <v>0.6423715527259012</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0.9394897098556042</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0.6394136222998187</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0.853998440656263</v>
+      </c>
+      <c r="Q257" t="n">
         <v>60.56606700729476</v>
       </c>
     </row>
@@ -12599,6 +14899,18 @@
         <v>199.266534622404</v>
       </c>
       <c r="M258" t="n">
+        <v>0.5033588072551085</v>
+      </c>
+      <c r="N258" t="n">
+        <v>0.6007978256698693</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0.5182875477519644</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0.6990163261676178</v>
+      </c>
+      <c r="Q258" t="n">
         <v>96.58377859588913</v>
       </c>
     </row>
@@ -12652,6 +14964,18 @@
         <v>196.027032077751</v>
       </c>
       <c r="M259" t="n">
+        <v>0.8174131735890285</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0.6629860256274435</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0.8423692643769854</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0.8228462283070879</v>
+      </c>
+      <c r="Q259" t="n">
         <v>137.9505819039528</v>
       </c>
     </row>
@@ -12705,6 +15029,18 @@
         <v>200</v>
       </c>
       <c r="M260" t="n">
+        <v>0.7714116916561566</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0.7720109454464555</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0.8155887005444008</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0.7899807321772639</v>
+      </c>
+      <c r="Q260" t="n">
         <v>131.3215089600104</v>
       </c>
     </row>
@@ -12758,6 +15094,18 @@
         <v>200</v>
       </c>
       <c r="M261" t="n">
+        <v>1.07198087489065</v>
+      </c>
+      <c r="N261" t="n">
+        <v>1.199289297607488</v>
+      </c>
+      <c r="O261" t="n">
+        <v>1.128609910494177</v>
+      </c>
+      <c r="P261" t="n">
+        <v>1.233082706766917</v>
+      </c>
+      <c r="Q261" t="n">
         <v>128.5814859056328</v>
       </c>
     </row>
@@ -12811,6 +15159,18 @@
         <v>200</v>
       </c>
       <c r="M262" t="n">
+        <v>0.7949253645598374</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0.9119105564743384</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0.796530427693932</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0.814569536423841</v>
+      </c>
+      <c r="Q262" t="n">
         <v>144.8946185474515</v>
       </c>
     </row>
@@ -12864,6 +15224,18 @@
         <v>69.3636115809701</v>
       </c>
       <c r="M263" t="n">
+        <v>0.6376713320022183</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0.7586009180317456</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0.6202153428308693</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0.656438989470018</v>
+      </c>
+      <c r="Q263" t="n">
         <v>65.54013671678976</v>
       </c>
     </row>
@@ -12917,6 +15289,18 @@
         <v>103.1243424058656</v>
       </c>
       <c r="M264" t="n">
+        <v>0.5562617950199628</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0.6994946087096505</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0.4554898791052577</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0.4766723931148578</v>
+      </c>
+      <c r="Q264" t="n">
         <v>98.68946232030373</v>
       </c>
     </row>
@@ -12970,6 +15354,18 @@
         <v>104.5038660583959</v>
       </c>
       <c r="M265" t="n">
+        <v>0.3232653871350063</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0.3274307984162803</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0.328734848481341</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0.3339597976985841</v>
+      </c>
+      <c r="Q265" t="n">
         <v>94.87451528276132</v>
       </c>
     </row>
@@ -13023,6 +15419,18 @@
         <v>183.8106896888022</v>
       </c>
       <c r="M266" t="n">
+        <v>0.8157747465146061</v>
+      </c>
+      <c r="N266" t="n">
+        <v>1.177598242560326</v>
+      </c>
+      <c r="O266" t="n">
+        <v>1.043493974235836</v>
+      </c>
+      <c r="P266" t="n">
+        <v>1.239998761816796</v>
+      </c>
+      <c r="Q266" t="n">
         <v>84.60849036193123</v>
       </c>
     </row>
@@ -13076,6 +15484,18 @@
         <v>200</v>
       </c>
       <c r="M267" t="n">
+        <v>0.840909930867532</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0.8725890866503054</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0.8376069541653399</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0.9761904761904763</v>
+      </c>
+      <c r="Q267" t="n">
         <v>136.7169591180488</v>
       </c>
     </row>
@@ -13129,6 +15549,18 @@
         <v>128.2424734098853</v>
       </c>
       <c r="M268" t="n">
+        <v>0.3793322764164702</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0.299302166337495</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0.2938483681760444</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0.254165043845994</v>
+      </c>
+      <c r="Q268" t="n">
         <v>117.030082044597</v>
       </c>
     </row>
@@ -13182,6 +15614,18 @@
         <v>15.96170623271637</v>
       </c>
       <c r="M269" t="n">
+        <v>0.4350646239472201</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0.8077024830157333</v>
+      </c>
+      <c r="O269" t="n">
+        <v>1.160188651689404</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0.4591708107768643</v>
+      </c>
+      <c r="Q269" t="n">
         <v>15.04439676494237</v>
       </c>
     </row>
@@ -13235,6 +15679,18 @@
         <v>38.13654046483583</v>
       </c>
       <c r="M270" t="n">
+        <v>0.2335631920140529</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0.5515711068602442</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0.858510835271867</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0.2830811243187917</v>
+      </c>
+      <c r="Q270" t="n">
         <v>31.07438395174653</v>
       </c>
     </row>
@@ -13288,6 +15744,18 @@
         <v>29.64716325384969</v>
       </c>
       <c r="M271" t="n">
+        <v>0.1857508985606814</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0.3756851406489205</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0.5026091693150885</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0.2185372590129753</v>
+      </c>
+      <c r="Q271" t="n">
         <v>25.74611683419902</v>
       </c>
     </row>
@@ -13341,6 +15809,18 @@
         <v>149.0335439857258</v>
       </c>
       <c r="M272" t="n">
+        <v>0.5835353762939055</v>
+      </c>
+      <c r="N272" t="n">
+        <v>0.7705455048482636</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0.5889415998996159</v>
+      </c>
+      <c r="P272" t="n">
+        <v>0.6753767707165687</v>
+      </c>
+      <c r="Q272" t="n">
         <v>102.4238315579823</v>
       </c>
     </row>
@@ -13394,6 +15874,18 @@
         <v>77.60370062523111</v>
       </c>
       <c r="M273" t="n">
+        <v>0.3500800703575624</v>
+      </c>
+      <c r="N273" t="n">
+        <v>0.4250529461775757</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0.4926140741671675</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0.348590149918133</v>
+      </c>
+      <c r="Q273" t="n">
         <v>66.62415922018562</v>
       </c>
     </row>
@@ -13447,6 +15939,18 @@
         <v>124.9431249402034</v>
       </c>
       <c r="M274" t="n">
+        <v>0.2980474803936629</v>
+      </c>
+      <c r="N274" t="n">
+        <v>0.3825808363409376</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0.3295602207721805</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0.380552598053949</v>
+      </c>
+      <c r="Q274" t="n">
         <v>85.58397821566523</v>
       </c>
     </row>
@@ -13500,6 +16004,18 @@
         <v>110.9180479560936</v>
       </c>
       <c r="M275" t="n">
+        <v>1.116157123165698</v>
+      </c>
+      <c r="N275" t="n">
+        <v>1.277853852754639</v>
+      </c>
+      <c r="O275" t="n">
+        <v>1.113069608497959</v>
+      </c>
+      <c r="P275" t="n">
+        <v>1.288379046521931</v>
+      </c>
+      <c r="Q275" t="n">
         <v>84.05465359366345</v>
       </c>
     </row>
@@ -13553,6 +16069,18 @@
         <v>200</v>
       </c>
       <c r="M276" t="n">
+        <v>0.8818019075772333</v>
+      </c>
+      <c r="N276" t="n">
+        <v>1.060363269800217</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0.9184320515504194</v>
+      </c>
+      <c r="P276" t="n">
+        <v>1.065663474692202</v>
+      </c>
+      <c r="Q276" t="n">
         <v>127.892523367874</v>
       </c>
     </row>
@@ -13606,6 +16134,18 @@
         <v>169.7206760380392</v>
       </c>
       <c r="M277" t="n">
+        <v>0.6102315870166403</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0.6787021139999347</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0.5784087041585355</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0.6626643240472104</v>
+      </c>
+      <c r="Q277" t="n">
         <v>118.4966280864306</v>
       </c>
     </row>
@@ -13659,6 +16199,18 @@
         <v>55.52941065664324</v>
       </c>
       <c r="M278" t="n">
+        <v>0.6428882224742702</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0.8133092798904633</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0.7963087205659256</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0.6118086052448098</v>
+      </c>
+      <c r="Q278" t="n">
         <v>55.33102664886087</v>
       </c>
     </row>
@@ -13712,6 +16264,18 @@
         <v>110.3476655703105</v>
       </c>
       <c r="M279" t="n">
+        <v>0.371423838339113</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0.3385603330318428</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0.3931339712927203</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0.2797291924201393</v>
+      </c>
+      <c r="Q279" t="n">
         <v>107.6932531241744</v>
       </c>
     </row>
@@ -13765,6 +16329,18 @@
         <v>115.8565936335611</v>
       </c>
       <c r="M280" t="n">
+        <v>0.6578865879878135</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0.8975247856653285</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0.7852298944846973</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0.7766057668694866</v>
+      </c>
+      <c r="Q280" t="n">
         <v>79.72415139355161</v>
       </c>
     </row>
@@ -13818,6 +16394,18 @@
         <v>95.39572965465925</v>
       </c>
       <c r="M281" t="n">
+        <v>0.9506964490576815</v>
+      </c>
+      <c r="N281" t="n">
+        <v>1.014801124214123</v>
+      </c>
+      <c r="O281" t="n">
+        <v>1.038945072516929</v>
+      </c>
+      <c r="P281" t="n">
+        <v>1.078269074617236</v>
+      </c>
+      <c r="Q281" t="n">
         <v>92.68891305408687</v>
       </c>
     </row>
@@ -13871,6 +16459,18 @@
         <v>138.7639265024128</v>
       </c>
       <c r="M282" t="n">
+        <v>0.4826164107498371</v>
+      </c>
+      <c r="N282" t="n">
+        <v>0.7007489000733184</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0.4895698889921585</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0.4634364861882697</v>
+      </c>
+      <c r="Q282" t="n">
         <v>117.7101091156265</v>
       </c>
     </row>
@@ -13924,6 +16524,18 @@
         <v>64.16235094681618</v>
       </c>
       <c r="M283" t="n">
+        <v>0.2978521543632051</v>
+      </c>
+      <c r="N283" t="n">
+        <v>0.3414706756860459</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0.3361198353020063</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0.3056034163627496</v>
+      </c>
+      <c r="Q283" t="n">
         <v>54.60316630179442</v>
       </c>
     </row>
@@ -13965,6 +16577,10 @@
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14004,6 +16620,10 @@
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14043,6 +16663,10 @@
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14082,6 +16706,10 @@
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14121,6 +16749,10 @@
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14160,6 +16792,10 @@
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14199,6 +16835,10 @@
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14238,6 +16878,10 @@
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14277,6 +16921,10 @@
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14316,6 +16964,10 @@
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14355,6 +17007,10 @@
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14394,6 +17050,10 @@
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14433,6 +17093,10 @@
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14472,6 +17136,10 @@
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14511,6 +17179,10 @@
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14550,6 +17222,10 @@
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14589,6 +17265,10 @@
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14628,6 +17308,10 @@
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14667,6 +17351,10 @@
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14706,6 +17394,10 @@
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14745,6 +17437,10 @@
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14784,6 +17480,10 @@
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14823,6 +17523,10 @@
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14862,6 +17566,10 @@
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14901,6 +17609,10 @@
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14940,6 +17652,10 @@
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14979,6 +17695,10 @@
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15018,6 +17738,10 @@
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15057,6 +17781,10 @@
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15096,6 +17824,10 @@
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15147,6 +17879,18 @@
         <v>46.31888825518345</v>
       </c>
       <c r="M314" t="n">
+        <v>0.4508685702768471</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0.5770012139279245</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0.465286398097716</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0.679967243055041</v>
+      </c>
+      <c r="Q314" t="n">
         <v>36.77262101215506</v>
       </c>
     </row>
@@ -15200,6 +17944,18 @@
         <v>90.69921131334431</v>
       </c>
       <c r="M315" t="n">
+        <v>1.050417558689313</v>
+      </c>
+      <c r="N315" t="n">
+        <v>1.608796446035823</v>
+      </c>
+      <c r="O315" t="n">
+        <v>2.866952688842529</v>
+      </c>
+      <c r="P315" t="n">
+        <v>5.874622091270426</v>
+      </c>
+      <c r="Q315" t="n">
         <v>30.67859068105952</v>
       </c>
     </row>
@@ -15253,6 +18009,18 @@
         <v>37.46315461611704</v>
       </c>
       <c r="M316" t="n">
+        <v>0.2384902381637455</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0.3457405042390501</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0.4292452742467616</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0.3020041090007478</v>
+      </c>
+      <c r="Q316" t="n">
         <v>30.0051905770257</v>
       </c>
     </row>
@@ -15306,6 +18074,18 @@
         <v>57.71525120895403</v>
       </c>
       <c r="M317" t="n">
+        <v>0.5395985094661678</v>
+      </c>
+      <c r="N317" t="n">
+        <v>1.785828571784391</v>
+      </c>
+      <c r="O317" t="n">
+        <v>2.002094523739497</v>
+      </c>
+      <c r="P317" t="n">
+        <v>2.342476696497458</v>
+      </c>
+      <c r="Q317" t="n">
         <v>18.45861727515264</v>
       </c>
     </row>
@@ -15359,6 +18139,18 @@
         <v>70.77848444920932</v>
       </c>
       <c r="M318" t="n">
+        <v>0.2034896007030427</v>
+      </c>
+      <c r="N318" t="n">
+        <v>0.5907411407752843</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0.581182654321204</v>
+      </c>
+      <c r="P318" t="n">
+        <v>0.7330910485790602</v>
+      </c>
+      <c r="Q318" t="n">
         <v>32.48225878972697</v>
       </c>
     </row>
@@ -15412,6 +18204,18 @@
         <v>53.20878373312041</v>
       </c>
       <c r="M319" t="n">
+        <v>0.4186453830577432</v>
+      </c>
+      <c r="N319" t="n">
+        <v>0.426095520038376</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0.5806634295638829</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0.5638643347431748</v>
+      </c>
+      <c r="Q319" t="n">
         <v>45.72072234726389</v>
       </c>
     </row>
@@ -15465,6 +18269,18 @@
         <v>42.86565285316097</v>
       </c>
       <c r="M320" t="n">
+        <v>0.3715814058530271</v>
+      </c>
+      <c r="N320" t="n">
+        <v>0.4876253496283554</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0.7019186693195074</v>
+      </c>
+      <c r="P320" t="n">
+        <v>0.4258098387914416</v>
+      </c>
+      <c r="Q320" t="n">
         <v>42.52091610548823</v>
       </c>
     </row>
@@ -15518,6 +18334,18 @@
         <v>55.66547558109725</v>
       </c>
       <c r="M321" t="n">
+        <v>0.3386071962883859</v>
+      </c>
+      <c r="N321" t="n">
+        <v>0.4089366977908878</v>
+      </c>
+      <c r="O321" t="n">
+        <v>0.4966199424821776</v>
+      </c>
+      <c r="P321" t="n">
+        <v>0.4924233769972484</v>
+      </c>
+      <c r="Q321" t="n">
         <v>42.81682878277621</v>
       </c>
     </row>
@@ -15571,6 +18399,18 @@
         <v>65.04154883954841</v>
       </c>
       <c r="M322" t="n">
+        <v>0.2479559476933842</v>
+      </c>
+      <c r="N322" t="n">
+        <v>0.4765808316455287</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0.494378702941688</v>
+      </c>
+      <c r="P322" t="n">
+        <v>0.8690469436602506</v>
+      </c>
+      <c r="Q322" t="n">
         <v>31.40856212876422</v>
       </c>
     </row>
@@ -15624,6 +18464,18 @@
         <v>86.47389235560937</v>
       </c>
       <c r="M323" t="n">
+        <v>0.3963255092819015</v>
+      </c>
+      <c r="N323" t="n">
+        <v>1.101364473483144</v>
+      </c>
+      <c r="O323" t="n">
+        <v>1.190143852051516</v>
+      </c>
+      <c r="P323" t="n">
+        <v>1.089689364817858</v>
+      </c>
+      <c r="Q323" t="n">
         <v>51.47454095555525</v>
       </c>
     </row>
@@ -15677,6 +18529,18 @@
         <v>74.32989582884704</v>
       </c>
       <c r="M324" t="n">
+        <v>0.3781036854142671</v>
+      </c>
+      <c r="N324" t="n">
+        <v>0.6423162383512216</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0.3637624430250099</v>
+      </c>
+      <c r="P324" t="n">
+        <v>0.8271779464533132</v>
+      </c>
+      <c r="Q324" t="n">
         <v>54.96446501486252</v>
       </c>
     </row>
@@ -15730,6 +18594,18 @@
         <v>46.36800926624585</v>
       </c>
       <c r="M325" t="n">
+        <v>0.2598475350324232</v>
+      </c>
+      <c r="N325" t="n">
+        <v>0.3711753577773378</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0.6731489599107356</v>
+      </c>
+      <c r="P325" t="n">
+        <v>0.2797443527341223</v>
+      </c>
+      <c r="Q325" t="n">
         <v>45.32437628043645</v>
       </c>
     </row>
@@ -15783,6 +18659,18 @@
         <v>62.64937372799514</v>
       </c>
       <c r="M326" t="n">
+        <v>0.3807176450697521</v>
+      </c>
+      <c r="N326" t="n">
+        <v>0.5017563599921097</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0.4834458100975091</v>
+      </c>
+      <c r="P326" t="n">
+        <v>0.9318839017358045</v>
+      </c>
+      <c r="Q326" t="n">
         <v>41.78056745188351</v>
       </c>
     </row>
@@ -15836,6 +18724,18 @@
         <v>36.21531592017715</v>
       </c>
       <c r="M327" t="n">
+        <v>0.322862851774778</v>
+      </c>
+      <c r="N327" t="n">
+        <v>0.3829178188692746</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0.7402200312984576</v>
+      </c>
+      <c r="P327" t="n">
+        <v>0.3199900954936826</v>
+      </c>
+      <c r="Q327" t="n">
         <v>35.94941471393788</v>
       </c>
     </row>
@@ -15889,6 +18789,18 @@
         <v>108.0441912405262</v>
       </c>
       <c r="M328" t="n">
+        <v>0.4617523569929864</v>
+      </c>
+      <c r="N328" t="n">
+        <v>0.6879049167415063</v>
+      </c>
+      <c r="O328" t="n">
+        <v>0.5247765578030212</v>
+      </c>
+      <c r="P328" t="n">
+        <v>0.4615756330485044</v>
+      </c>
+      <c r="Q328" t="n">
         <v>100.0320316293014</v>
       </c>
     </row>
@@ -15942,6 +18854,18 @@
         <v>123.2112795373372</v>
       </c>
       <c r="M329" t="n">
+        <v>0.7033622390565423</v>
+      </c>
+      <c r="N329" t="n">
+        <v>1.160817426778423</v>
+      </c>
+      <c r="O329" t="n">
+        <v>1.057085989511315</v>
+      </c>
+      <c r="P329" t="n">
+        <v>1.156823771195449</v>
+      </c>
+      <c r="Q329" t="n">
         <v>55.24764638527707</v>
       </c>
     </row>
@@ -15995,6 +18919,18 @@
         <v>200</v>
       </c>
       <c r="M330" t="n">
+        <v>0.6744523326898315</v>
+      </c>
+      <c r="N330" t="n">
+        <v>0.8151423427463497</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0.737690032290728</v>
+      </c>
+      <c r="P330" t="n">
+        <v>0.8322056833558863</v>
+      </c>
+      <c r="Q330" t="n">
         <v>112.1546810150188</v>
       </c>
     </row>
@@ -16048,6 +18984,18 @@
         <v>147.8964180670695</v>
       </c>
       <c r="M331" t="n">
+        <v>0.4832168873366318</v>
+      </c>
+      <c r="N331" t="n">
+        <v>0.548017825302065</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0.4317905848569702</v>
+      </c>
+      <c r="P331" t="n">
+        <v>0.4627980257362326</v>
+      </c>
+      <c r="Q331" t="n">
         <v>101.6772432478667</v>
       </c>
     </row>
@@ -16101,6 +19049,18 @@
         <v>107.7666594831524</v>
       </c>
       <c r="M332" t="n">
+        <v>0.5874539621168943</v>
+      </c>
+      <c r="N332" t="n">
+        <v>0.7492321285005537</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0.660326038345017</v>
+      </c>
+      <c r="P332" t="n">
+        <v>0.6584503052074618</v>
+      </c>
+      <c r="Q332" t="n">
         <v>91.06571891773466</v>
       </c>
     </row>
@@ -16154,6 +19114,18 @@
         <v>31.33055232792077</v>
       </c>
       <c r="M333" t="n">
+        <v>0.3435129491488734</v>
+      </c>
+      <c r="N333" t="n">
+        <v>0.4185902093029827</v>
+      </c>
+      <c r="O333" t="n">
+        <v>1.4221636855648</v>
+      </c>
+      <c r="P333" t="n">
+        <v>0.5513123036211611</v>
+      </c>
+      <c r="Q333" t="n">
         <v>21.13647018864575</v>
       </c>
     </row>
@@ -16207,6 +19179,18 @@
         <v>54.23526434531124</v>
       </c>
       <c r="M334" t="n">
+        <v>0.1295041740494585</v>
+      </c>
+      <c r="N334" t="n">
+        <v>0.1732461686112731</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0.146721068732649</v>
+      </c>
+      <c r="P334" t="n">
+        <v>0.1613110933282751</v>
+      </c>
+      <c r="Q334" t="n">
         <v>48.38469322753042</v>
       </c>
     </row>
@@ -16260,6 +19244,18 @@
         <v>67.25017778286251</v>
       </c>
       <c r="M335" t="n">
+        <v>0.1210114012123513</v>
+      </c>
+      <c r="N335" t="n">
+        <v>0.1457558528286318</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0.2734969749060554</v>
+      </c>
+      <c r="P335" t="n">
+        <v>0.1684238062134517</v>
+      </c>
+      <c r="Q335" t="n">
         <v>54.28971128059189</v>
       </c>
     </row>
@@ -16313,6 +19309,18 @@
         <v>83.15591706793485</v>
       </c>
       <c r="M336" t="n">
+        <v>1.336476913002625</v>
+      </c>
+      <c r="N336" t="n">
+        <v>1.238518037274083</v>
+      </c>
+      <c r="O336" t="n">
+        <v>1.35297191171122</v>
+      </c>
+      <c r="P336" t="n">
+        <v>1.44356735141489</v>
+      </c>
+      <c r="Q336" t="n">
         <v>73.8569051239155</v>
       </c>
     </row>
@@ -16366,6 +19374,18 @@
         <v>68.03307483742823</v>
       </c>
       <c r="M337" t="n">
+        <v>0.2727205645792258</v>
+      </c>
+      <c r="N337" t="n">
+        <v>0.3656592060680761</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0.2989842761156919</v>
+      </c>
+      <c r="P337" t="n">
+        <v>0.2999507755905753</v>
+      </c>
+      <c r="Q337" t="n">
         <v>58.76460082616407</v>
       </c>
     </row>
@@ -16419,6 +19439,18 @@
         <v>76.20844107307784</v>
       </c>
       <c r="M338" t="n">
+        <v>1.009269968139774</v>
+      </c>
+      <c r="N338" t="n">
+        <v>1.17196769210065</v>
+      </c>
+      <c r="O338" t="n">
+        <v>1.091297248177458</v>
+      </c>
+      <c r="P338" t="n">
+        <v>1.47102171541058</v>
+      </c>
+      <c r="Q338" t="n">
         <v>67.80058606926306</v>
       </c>
     </row>
@@ -16472,6 +19504,18 @@
         <v>92.30114233991516</v>
       </c>
       <c r="M339" t="n">
+        <v>0.2838685135230369</v>
+      </c>
+      <c r="N339" t="n">
+        <v>0.3238320808718255</v>
+      </c>
+      <c r="O339" t="n">
+        <v>0.2931956433494415</v>
+      </c>
+      <c r="P339" t="n">
+        <v>0.3555975841736566</v>
+      </c>
+      <c r="Q339" t="n">
         <v>87.3799490296847</v>
       </c>
     </row>
@@ -16525,6 +19569,18 @@
         <v>54.0180871606963</v>
       </c>
       <c r="M340" t="n">
+        <v>0.8110657370030397</v>
+      </c>
+      <c r="N340" t="n">
+        <v>1.215960060028445</v>
+      </c>
+      <c r="O340" t="n">
+        <v>1.068283076496065</v>
+      </c>
+      <c r="P340" t="n">
+        <v>0.8603357679466302</v>
+      </c>
+      <c r="Q340" t="n">
         <v>50.75918004446772</v>
       </c>
     </row>
@@ -16578,6 +19634,18 @@
         <v>85.44267051365514</v>
       </c>
       <c r="M341" t="n">
+        <v>0.4886665275101726</v>
+      </c>
+      <c r="N341" t="n">
+        <v>0.5812703296032669</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0.5513132587205374</v>
+      </c>
+      <c r="P341" t="n">
+        <v>0.4966163506311503</v>
+      </c>
+      <c r="Q341" t="n">
         <v>79.70873046654407</v>
       </c>
     </row>
@@ -16631,6 +19699,18 @@
         <v>80.99552925976795</v>
       </c>
       <c r="M342" t="n">
+        <v>0.3841300288545666</v>
+      </c>
+      <c r="N342" t="n">
+        <v>0.5425369126142109</v>
+      </c>
+      <c r="O342" t="n">
+        <v>0.3894318466576467</v>
+      </c>
+      <c r="P342" t="n">
+        <v>0.3876475709868183</v>
+      </c>
+      <c r="Q342" t="n">
         <v>75.38790273863978</v>
       </c>
     </row>
@@ -16684,6 +19764,18 @@
         <v>62.46601918999117</v>
       </c>
       <c r="M343" t="n">
+        <v>0.6455875318912198</v>
+      </c>
+      <c r="N343" t="n">
+        <v>0.9556456418330385</v>
+      </c>
+      <c r="O343" t="n">
+        <v>1.213888485289873</v>
+      </c>
+      <c r="P343" t="n">
+        <v>0.7920430799688709</v>
+      </c>
+      <c r="Q343" t="n">
         <v>49.10990735112642</v>
       </c>
     </row>
@@ -16737,6 +19829,18 @@
         <v>79.76146499886427</v>
       </c>
       <c r="M344" t="n">
+        <v>0.4481835418977841</v>
+      </c>
+      <c r="N344" t="n">
+        <v>0.613468893432116</v>
+      </c>
+      <c r="O344" t="n">
+        <v>0.4891026043879896</v>
+      </c>
+      <c r="P344" t="n">
+        <v>0.5247499816390938</v>
+      </c>
+      <c r="Q344" t="n">
         <v>63.70632129889756</v>
       </c>
     </row>
@@ -16790,6 +19894,18 @@
         <v>147.0875155823664</v>
       </c>
       <c r="M345" t="n">
+        <v>0.3689534823228903</v>
+      </c>
+      <c r="N345" t="n">
+        <v>0.5342642361798509</v>
+      </c>
+      <c r="O345" t="n">
+        <v>0.414200307059212</v>
+      </c>
+      <c r="P345" t="n">
+        <v>0.4197670817107631</v>
+      </c>
+      <c r="Q345" t="n">
         <v>106.6313030414071</v>
       </c>
     </row>
@@ -16843,6 +19959,18 @@
         <v>158.1730450913396</v>
       </c>
       <c r="M346" t="n">
+        <v>0.3197790164759707</v>
+      </c>
+      <c r="N346" t="n">
+        <v>0.3652949742727167</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0.3083508455931132</v>
+      </c>
+      <c r="P346" t="n">
+        <v>0.3897096835988693</v>
+      </c>
+      <c r="Q346" t="n">
         <v>107.7598662080844</v>
       </c>
     </row>
@@ -16896,6 +20024,18 @@
         <v>200</v>
       </c>
       <c r="M347" t="n">
+        <v>0.1970127311090964</v>
+      </c>
+      <c r="N347" t="n">
+        <v>0.2005978059142367</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0.1912322794440926</v>
+      </c>
+      <c r="P347" t="n">
+        <v>0.2231899836690256</v>
+      </c>
+      <c r="Q347" t="n">
         <v>113.7228303204417</v>
       </c>
     </row>
@@ -16949,6 +20089,18 @@
         <v>107.1752281898208</v>
       </c>
       <c r="M348" t="n">
+        <v>0.4343915216769101</v>
+      </c>
+      <c r="N348" t="n">
+        <v>0.3413761744187302</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0.2650098414591614</v>
+      </c>
+      <c r="P348" t="n">
+        <v>0.5293655428372891</v>
+      </c>
+      <c r="Q348" t="n">
         <v>99.40580099722651</v>
       </c>
     </row>
@@ -17002,6 +20154,18 @@
         <v>46.72419656255779</v>
       </c>
       <c r="M349" t="n">
+        <v>0.6491916140618627</v>
+      </c>
+      <c r="N349" t="n">
+        <v>0.853647569413331</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0.7770112263312405</v>
+      </c>
+      <c r="P349" t="n">
+        <v>0.7031522310050002</v>
+      </c>
+      <c r="Q349" t="n">
         <v>43.26147796055416</v>
       </c>
     </row>
@@ -17055,6 +20219,18 @@
         <v>57.33545907832239</v>
       </c>
       <c r="M350" t="n">
+        <v>0.3113906219216222</v>
+      </c>
+      <c r="N350" t="n">
+        <v>0.4602528843927808</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0.3804579954746297</v>
+      </c>
+      <c r="P350" t="n">
+        <v>0.3317608997740304</v>
+      </c>
+      <c r="Q350" t="n">
         <v>54.71992513309608</v>
       </c>
     </row>
@@ -17108,6 +20284,18 @@
         <v>82.70459046747266</v>
       </c>
       <c r="M351" t="n">
+        <v>0.334578429539189</v>
+      </c>
+      <c r="N351" t="n">
+        <v>0.4269431307457797</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0.4832919357112265</v>
+      </c>
+      <c r="P351" t="n">
+        <v>0.3580083144185144</v>
+      </c>
+      <c r="Q351" t="n">
         <v>77.84369667815881</v>
       </c>
     </row>
@@ -17161,6 +20349,18 @@
         <v>33.53246264308181</v>
       </c>
       <c r="M352" t="n">
+        <v>0.4186075499085875</v>
+      </c>
+      <c r="N352" t="n">
+        <v>0.5527161472319062</v>
+      </c>
+      <c r="O352" t="n">
+        <v>1.796499252523183</v>
+      </c>
+      <c r="P352" t="n">
+        <v>0.9570961275570429</v>
+      </c>
+      <c r="Q352" t="n">
         <v>12.74242960309127</v>
       </c>
     </row>
@@ -17214,6 +20414,18 @@
         <v>27.91219358414629</v>
       </c>
       <c r="M353" t="n">
+        <v>0.09411405048396684</v>
+      </c>
+      <c r="N353" t="n">
+        <v>0.1102818480620861</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0.4096269938657115</v>
+      </c>
+      <c r="P353" t="n">
+        <v>0.09600821904842145</v>
+      </c>
+      <c r="Q353" t="n">
         <v>27.88292786899346</v>
       </c>
     </row>
@@ -17267,6 +20479,18 @@
         <v>119.6288998112822</v>
       </c>
       <c r="M354" t="n">
+        <v>0.9411283748639084</v>
+      </c>
+      <c r="N354" t="n">
+        <v>0.9403785392837417</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0.9550509798060167</v>
+      </c>
+      <c r="P354" t="n">
+        <v>1.020833821977028</v>
+      </c>
+      <c r="Q354" t="n">
         <v>99.62936888626999</v>
       </c>
     </row>
@@ -17320,6 +20544,18 @@
         <v>107.4429032306914</v>
       </c>
       <c r="M355" t="n">
+        <v>0.1811861327389599</v>
+      </c>
+      <c r="N355" t="n">
+        <v>0.1363067821928199</v>
+      </c>
+      <c r="O355" t="n">
+        <v>0.1968704859684761</v>
+      </c>
+      <c r="P355" t="n">
+        <v>0.1698027553116857</v>
+      </c>
+      <c r="Q355" t="n">
         <v>91.28429245655491</v>
       </c>
     </row>
@@ -17373,6 +20609,18 @@
         <v>71.63910422366816</v>
       </c>
       <c r="M356" t="n">
+        <v>0.4167919908185701</v>
+      </c>
+      <c r="N356" t="n">
+        <v>0.6322073139693037</v>
+      </c>
+      <c r="O356" t="n">
+        <v>0.8017722092121863</v>
+      </c>
+      <c r="P356" t="n">
+        <v>0.5671367608321887</v>
+      </c>
+      <c r="Q356" t="n">
         <v>49.41408585582083</v>
       </c>
     </row>
@@ -17426,6 +20674,18 @@
         <v>93.81015884369116</v>
       </c>
       <c r="M357" t="n">
+        <v>0.2288023333859732</v>
+      </c>
+      <c r="N357" t="n">
+        <v>0.2317402240718686</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0.3221365805844809</v>
+      </c>
+      <c r="P357" t="n">
+        <v>0.2343331201683543</v>
+      </c>
+      <c r="Q357" t="n">
         <v>79.1060330084559</v>
       </c>
     </row>
@@ -17479,6 +20739,18 @@
         <v>122.7166383513979</v>
       </c>
       <c r="M358" t="n">
+        <v>0.2226058941312427</v>
+      </c>
+      <c r="N358" t="n">
+        <v>0.3623252188434248</v>
+      </c>
+      <c r="O358" t="n">
+        <v>0.2429837464808083</v>
+      </c>
+      <c r="P358" t="n">
+        <v>0.3074661232183567</v>
+      </c>
+      <c r="Q358" t="n">
         <v>75.66439549162119</v>
       </c>
     </row>
@@ -17532,6 +20804,18 @@
         <v>111.0995148548672</v>
       </c>
       <c r="M359" t="n">
+        <v>1.086855032365653</v>
+      </c>
+      <c r="N359" t="n">
+        <v>2.865984653673737</v>
+      </c>
+      <c r="O359" t="n">
+        <v>1.286027781879889</v>
+      </c>
+      <c r="P359" t="n">
+        <v>3.017637395941263</v>
+      </c>
+      <c r="Q359" t="n">
         <v>68.12013049592807</v>
       </c>
     </row>
@@ -17585,6 +20869,18 @@
         <v>105.5704849717661</v>
       </c>
       <c r="M360" t="n">
+        <v>0.333791820959764</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0.2995592468978827</v>
+      </c>
+      <c r="O360" t="n">
+        <v>0.2459742152763944</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0.3859230366113445</v>
+      </c>
+      <c r="Q360" t="n">
         <v>100.9565799523856</v>
       </c>
     </row>
@@ -17638,6 +20934,18 @@
         <v>174.0033354676006</v>
       </c>
       <c r="M361" t="n">
+        <v>0.6501307019059819</v>
+      </c>
+      <c r="N361" t="n">
+        <v>0.7021821391991797</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0.7898814174790946</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0.818211297761324</v>
+      </c>
+      <c r="Q361" t="n">
         <v>103.9245822529134</v>
       </c>
     </row>
@@ -17691,6 +20999,18 @@
         <v>186.0387365089735</v>
       </c>
       <c r="M362" t="n">
+        <v>0.5371162217075679</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0.5111483647727647</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0.4979970164554199</v>
+      </c>
+      <c r="P362" t="n">
+        <v>0.5281894632930764</v>
+      </c>
+      <c r="Q362" t="n">
         <v>127.2098651223455</v>
       </c>
     </row>
@@ -17744,6 +21064,18 @@
         <v>76.2416047939704</v>
       </c>
       <c r="M363" t="n">
+        <v>0.7350433243162732</v>
+      </c>
+      <c r="N363" t="n">
+        <v>0.6766280989567887</v>
+      </c>
+      <c r="O363" t="n">
+        <v>0.8878903900378232</v>
+      </c>
+      <c r="P363" t="n">
+        <v>0.7551972990284879</v>
+      </c>
+      <c r="Q363" t="n">
         <v>75.8357092011637</v>
       </c>
     </row>
@@ -17797,6 +21129,18 @@
         <v>105.3541768114061</v>
       </c>
       <c r="M364" t="n">
+        <v>0.1832019402316229</v>
+      </c>
+      <c r="N364" t="n">
+        <v>0.2220163900647227</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0.2323654424628325</v>
+      </c>
+      <c r="P364" t="n">
+        <v>0.2106173634801934</v>
+      </c>
+      <c r="Q364" t="n">
         <v>85.8619265072969</v>
       </c>
     </row>
@@ -17850,6 +21194,18 @@
         <v>45.06325883981478</v>
       </c>
       <c r="M365" t="n">
+        <v>0.1717443375935556</v>
+      </c>
+      <c r="N365" t="n">
+        <v>0.2610751941368424</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0.3779879269036754</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0.1898170038498116</v>
+      </c>
+      <c r="Q365" t="n">
         <v>41.91311186688556</v>
       </c>
     </row>
@@ -17903,6 +21259,18 @@
         <v>75.12594715582547</v>
       </c>
       <c r="M366" t="n">
+        <v>1.24875733635765</v>
+      </c>
+      <c r="N366" t="n">
+        <v>1.344904730628673</v>
+      </c>
+      <c r="O366" t="n">
+        <v>1.983336849816667</v>
+      </c>
+      <c r="P366" t="n">
+        <v>1.390624928926671</v>
+      </c>
+      <c r="Q366" t="n">
         <v>63.49960740699922</v>
       </c>
     </row>
@@ -17956,6 +21324,18 @@
         <v>110.4564566198569</v>
       </c>
       <c r="M367" t="n">
+        <v>0.3137441510730697</v>
+      </c>
+      <c r="N367" t="n">
+        <v>0.3551990313008684</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0.4128251255406509</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0.3620251404683079</v>
+      </c>
+      <c r="Q367" t="n">
         <v>87.94751552804215</v>
       </c>
     </row>
@@ -18009,6 +21389,18 @@
         <v>39.87420641461119</v>
       </c>
       <c r="M368" t="n">
+        <v>0.6190131607365561</v>
+      </c>
+      <c r="N368" t="n">
+        <v>0.9296837852616245</v>
+      </c>
+      <c r="O368" t="n">
+        <v>1.22459848175575</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0.6241613497164953</v>
+      </c>
+      <c r="Q368" t="n">
         <v>38.25681943526697</v>
       </c>
     </row>
@@ -18062,6 +21454,18 @@
         <v>48.57634876129747</v>
       </c>
       <c r="M369" t="n">
+        <v>0.3865848822440527</v>
+      </c>
+      <c r="N369" t="n">
+        <v>0.4478466752222714</v>
+      </c>
+      <c r="O369" t="n">
+        <v>0.5158960342153507</v>
+      </c>
+      <c r="P369" t="n">
+        <v>0.4041554127481565</v>
+      </c>
+      <c r="Q369" t="n">
         <v>47.95054790989123</v>
       </c>
     </row>
@@ -18115,6 +21519,18 @@
         <v>101.0682861927997</v>
       </c>
       <c r="M370" t="n">
+        <v>0.837095352869795</v>
+      </c>
+      <c r="N370" t="n">
+        <v>0.9294854650703027</v>
+      </c>
+      <c r="O370" t="n">
+        <v>0.8718485005849007</v>
+      </c>
+      <c r="P370" t="n">
+        <v>0.9804408861083734</v>
+      </c>
+      <c r="Q370" t="n">
         <v>78.49200445275744</v>
       </c>
     </row>
@@ -18168,6 +21584,18 @@
         <v>143.8371763293557</v>
       </c>
       <c r="M371" t="n">
+        <v>0.573491115276645</v>
+      </c>
+      <c r="N371" t="n">
+        <v>0.6656175148837704</v>
+      </c>
+      <c r="O371" t="n">
+        <v>0.6086265841785888</v>
+      </c>
+      <c r="P371" t="n">
+        <v>0.6481709997950585</v>
+      </c>
+      <c r="Q371" t="n">
         <v>117.2211072283996</v>
       </c>
     </row>
@@ -18221,6 +21649,18 @@
         <v>194.8968258847096</v>
       </c>
       <c r="M372" t="n">
+        <v>0.9440003548159701</v>
+      </c>
+      <c r="N372" t="n">
+        <v>0.8290715715483173</v>
+      </c>
+      <c r="O372" t="n">
+        <v>1.002490464726012</v>
+      </c>
+      <c r="P372" t="n">
+        <v>1.006971407498978</v>
+      </c>
+      <c r="Q372" t="n">
         <v>132.7578586599289</v>
       </c>
     </row>
@@ -18274,6 +21714,18 @@
         <v>93.12364228365689</v>
       </c>
       <c r="M373" t="n">
+        <v>0.568194887731465</v>
+      </c>
+      <c r="N373" t="n">
+        <v>0.4194304537147444</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0.431607808710842</v>
+      </c>
+      <c r="P373" t="n">
+        <v>0.3009694917877639</v>
+      </c>
+      <c r="Q373" t="n">
         <v>93.12364228365689</v>
       </c>
     </row>
@@ -18327,6 +21779,18 @@
         <v>33.69607704131863</v>
       </c>
       <c r="M374" t="n">
+        <v>0.5983060711803257</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0.8466431781169581</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0.9495719566582154</v>
+      </c>
+      <c r="P374" t="n">
+        <v>0.5711386493718532</v>
+      </c>
+      <c r="Q374" t="n">
         <v>33.69607704131863</v>
       </c>
     </row>
@@ -18380,6 +21844,18 @@
         <v>61.5181484263549</v>
       </c>
       <c r="M375" t="n">
+        <v>0.5341376760411619</v>
+      </c>
+      <c r="N375" t="n">
+        <v>0.7401265752065583</v>
+      </c>
+      <c r="O375" t="n">
+        <v>0.6038893278430219</v>
+      </c>
+      <c r="P375" t="n">
+        <v>0.3866442532278568</v>
+      </c>
+      <c r="Q375" t="n">
         <v>61.5181484263549</v>
       </c>
     </row>
@@ -18433,6 +21909,18 @@
         <v>51.70168576961532</v>
       </c>
       <c r="M376" t="n">
+        <v>0.6044548896581378</v>
+      </c>
+      <c r="N376" t="n">
+        <v>0.2936195934747563</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0.452580013997308</v>
+      </c>
+      <c r="P376" t="n">
+        <v>0.2473992936158512</v>
+      </c>
+      <c r="Q376" t="n">
         <v>51.70168576961532</v>
       </c>
     </row>
@@ -18486,6 +21974,18 @@
         <v>98.21385284081884</v>
       </c>
       <c r="M377" t="n">
+        <v>0.6256973299487033</v>
+      </c>
+      <c r="N377" t="n">
+        <v>0.6565602336436261</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0.5919565773593969</v>
+      </c>
+      <c r="P377" t="n">
+        <v>0.5783166083959221</v>
+      </c>
+      <c r="Q377" t="n">
         <v>98.21385284081884</v>
       </c>
     </row>
@@ -18539,6 +22039,18 @@
         <v>45.88567633150781</v>
       </c>
       <c r="M378" t="n">
+        <v>0.5102071345549269</v>
+      </c>
+      <c r="N378" t="n">
+        <v>0.9068218915111488</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0.6498769117391159</v>
+      </c>
+      <c r="P378" t="n">
+        <v>0.4973285861814409</v>
+      </c>
+      <c r="Q378" t="n">
         <v>45.88567633150781</v>
       </c>
     </row>
@@ -18580,6 +22092,10 @@
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr"/>
       <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
+      <c r="O379" t="inlineStr"/>
+      <c r="P379" t="inlineStr"/>
+      <c r="Q379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -18619,6 +22135,10 @@
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
       <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr"/>
+      <c r="P380" t="inlineStr"/>
+      <c r="Q380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -18658,6 +22178,10 @@
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr"/>
       <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr"/>
+      <c r="P381" t="inlineStr"/>
+      <c r="Q381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -18697,6 +22221,10 @@
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr"/>
       <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr"/>
+      <c r="P382" t="inlineStr"/>
+      <c r="Q382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -18736,6 +22264,10 @@
       <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr"/>
       <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
+      <c r="O383" t="inlineStr"/>
+      <c r="P383" t="inlineStr"/>
+      <c r="Q383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -18775,6 +22307,10 @@
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr"/>
       <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -18814,6 +22350,10 @@
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr"/>
+      <c r="Q385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -18853,6 +22393,10 @@
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
       <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr"/>
+      <c r="Q386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -18892,6 +22436,10 @@
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
       <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr"/>
+      <c r="Q387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -18943,6 +22491,18 @@
         <v>21.38331292671888</v>
       </c>
       <c r="M388" t="n">
+        <v>1.020054693102613</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0.5667670134590224</v>
+      </c>
+      <c r="O388" t="n">
+        <v>2.074032395121065</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0.4616302658536202</v>
+      </c>
+      <c r="Q388" t="n">
         <v>21.38331292671888</v>
       </c>
     </row>
@@ -18996,6 +22556,18 @@
         <v>36.61493448166976</v>
       </c>
       <c r="M389" t="n">
+        <v>0.2070619432807486</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0.344102259956361</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0.5693830880435606</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0.1960293669607654</v>
+      </c>
+      <c r="Q389" t="n">
         <v>36.61493448166976</v>
       </c>
     </row>
@@ -19049,6 +22621,18 @@
         <v>35.34934078732108</v>
       </c>
       <c r="M390" t="n">
+        <v>0.4126653061889282</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0.3027707995286087</v>
+      </c>
+      <c r="O390" t="n">
+        <v>0.8001621149769298</v>
+      </c>
+      <c r="P390" t="n">
+        <v>0.2372835777138725</v>
+      </c>
+      <c r="Q390" t="n">
         <v>35.34934078732108</v>
       </c>
     </row>
@@ -19102,6 +22686,18 @@
         <v>11.71211766648405</v>
       </c>
       <c r="M391" t="n">
+        <v>2.208629347279612</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0.7921505058911695</v>
+      </c>
+      <c r="O391" t="n">
+        <v>3.389744949316661</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0.5205779696997164</v>
+      </c>
+      <c r="Q391" t="n">
         <v>11.71211766648405</v>
       </c>
     </row>
@@ -19155,6 +22751,18 @@
         <v>25.67320006258615</v>
       </c>
       <c r="M392" t="n">
+        <v>0.7147935563099354</v>
+      </c>
+      <c r="N392" t="n">
+        <v>0.2900284453697967</v>
+      </c>
+      <c r="O392" t="n">
+        <v>1.29519991069198</v>
+      </c>
+      <c r="P392" t="n">
+        <v>0.282646048126059</v>
+      </c>
+      <c r="Q392" t="n">
         <v>25.67320006258615</v>
       </c>
     </row>
@@ -19208,6 +22816,18 @@
         <v>37.5459079175119</v>
       </c>
       <c r="M393" t="n">
+        <v>0.5658614432905642</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0.5539314547436145</v>
+      </c>
+      <c r="O393" t="n">
+        <v>1.453777965386239</v>
+      </c>
+      <c r="P393" t="n">
+        <v>0.5081187847463631</v>
+      </c>
+      <c r="Q393" t="n">
         <v>37.5459079175119</v>
       </c>
     </row>
@@ -19261,6 +22881,18 @@
         <v>21.91120295081257</v>
       </c>
       <c r="M394" t="n">
+        <v>2.043196447944043</v>
+      </c>
+      <c r="N394" t="n">
+        <v>1.10068953786601</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0.9612893017532146</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0.7456258522931477</v>
+      </c>
+      <c r="Q394" t="n">
         <v>21.91120295081257</v>
       </c>
     </row>
@@ -19314,6 +22946,18 @@
         <v>39.97144501298249</v>
       </c>
       <c r="M395" t="n">
+        <v>0.5333321230118296</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0.5989286029391677</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0.8286836344828632</v>
+      </c>
+      <c r="P395" t="n">
+        <v>0.4140794297110551</v>
+      </c>
+      <c r="Q395" t="n">
         <v>39.97144501298249</v>
       </c>
     </row>
@@ -19367,6 +23011,18 @@
         <v>32.96466542480608</v>
       </c>
       <c r="M396" t="n">
+        <v>0.4521778359455339</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0.669435663779501</v>
+      </c>
+      <c r="O396" t="n">
+        <v>1.073546700986111</v>
+      </c>
+      <c r="P396" t="n">
+        <v>0.4414456783172954</v>
+      </c>
+      <c r="Q396" t="n">
         <v>32.96466542480608</v>
       </c>
     </row>
@@ -19420,6 +23076,18 @@
         <v>21.01673129205267</v>
       </c>
       <c r="M397" t="n">
+        <v>2.510837078478999</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0.8450430349938787</v>
+      </c>
+      <c r="O397" t="n">
+        <v>2.175391648796167</v>
+      </c>
+      <c r="P397" t="n">
+        <v>0.7613050238800553</v>
+      </c>
+      <c r="Q397" t="n">
         <v>21.01673129205267</v>
       </c>
     </row>
@@ -19473,6 +23141,18 @@
         <v>42.19441167205013</v>
       </c>
       <c r="M398" t="n">
+        <v>0.8492092489140629</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0.6137826406654238</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0.9041997173493337</v>
+      </c>
+      <c r="P398" t="n">
+        <v>0.4483047306706729</v>
+      </c>
+      <c r="Q398" t="n">
         <v>42.19441167205013</v>
       </c>
     </row>
@@ -19526,6 +23206,18 @@
         <v>15.76751034674692</v>
       </c>
       <c r="M399" t="n">
+        <v>1.388833085607498</v>
+      </c>
+      <c r="N399" t="n">
+        <v>0.9626385442744847</v>
+      </c>
+      <c r="O399" t="n">
+        <v>2.033740738144528</v>
+      </c>
+      <c r="P399" t="n">
+        <v>0.5520121165892035</v>
+      </c>
+      <c r="Q399" t="n">
         <v>15.76751034674692</v>
       </c>
     </row>
@@ -19579,6 +23271,18 @@
         <v>19.07247003842105</v>
       </c>
       <c r="M400" t="n">
+        <v>2.080903971328945</v>
+      </c>
+      <c r="N400" t="n">
+        <v>1.026016803147045</v>
+      </c>
+      <c r="O400" t="n">
+        <v>1.192975468804622</v>
+      </c>
+      <c r="P400" t="n">
+        <v>0.8392012343461679</v>
+      </c>
+      <c r="Q400" t="n">
         <v>19.07247003842105</v>
       </c>
     </row>
@@ -19632,6 +23336,18 @@
         <v>36.80731291795723</v>
       </c>
       <c r="M401" t="n">
+        <v>0.7576017670988273</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0.475632852227248</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0.8364314961703201</v>
+      </c>
+      <c r="P401" t="n">
+        <v>0.4862619178747668</v>
+      </c>
+      <c r="Q401" t="n">
         <v>36.80731291795723</v>
       </c>
     </row>
@@ -19685,6 +23401,18 @@
         <v>13.63713521334846</v>
       </c>
       <c r="M402" t="n">
+        <v>2.516993794418864</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0.9450162202004487</v>
+      </c>
+      <c r="O402" t="n">
+        <v>4.551027126389426</v>
+      </c>
+      <c r="P402" t="n">
+        <v>0.6423734367628101</v>
+      </c>
+      <c r="Q402" t="n">
         <v>13.63713521334846</v>
       </c>
     </row>
@@ -19738,6 +23466,18 @@
         <v>37.02531398771454</v>
       </c>
       <c r="M403" t="n">
+        <v>0.6700108961903162</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0.5139560972019354</v>
+      </c>
+      <c r="O403" t="n">
+        <v>1.422637450496456</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0.5212477957750771</v>
+      </c>
+      <c r="Q403" t="n">
         <v>37.02531398771454</v>
       </c>
     </row>
@@ -19791,6 +23531,18 @@
         <v>27.63742222200863</v>
       </c>
       <c r="M404" t="n">
+        <v>0.723067430733296</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0.4607841274863926</v>
+      </c>
+      <c r="O404" t="n">
+        <v>1.39633699578468</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0.2955788911231727</v>
+      </c>
+      <c r="Q404" t="n">
         <v>27.63742222200863</v>
       </c>
     </row>
@@ -19844,6 +23596,18 @@
         <v>36.58180252632918</v>
       </c>
       <c r="M405" t="n">
+        <v>0.3047167454379853</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0.4305365856796169</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0.2849481511146357</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0.2800397293082332</v>
+      </c>
+      <c r="Q405" t="n">
         <v>36.58180252632918</v>
       </c>
     </row>
@@ -19897,6 +23661,18 @@
         <v>32.18367750921999</v>
       </c>
       <c r="M406" t="n">
+        <v>0.5785840903816114</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0.3039087619287513</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0.3531947912263751</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0.3043609501644202</v>
+      </c>
+      <c r="Q406" t="n">
         <v>32.18367750921999</v>
       </c>
     </row>
@@ -19950,6 +23726,18 @@
         <v>35.3895880392562</v>
       </c>
       <c r="M407" t="n">
+        <v>0.3475938385492333</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0.3727551505138199</v>
+      </c>
+      <c r="O407" t="n">
+        <v>1.17500726434954</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0.3452810511357737</v>
+      </c>
+      <c r="Q407" t="n">
         <v>35.3895880392562</v>
       </c>
     </row>
@@ -20003,6 +23791,18 @@
         <v>20.26238212970023</v>
       </c>
       <c r="M408" t="n">
+        <v>0.7825240923009829</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0.2765405865335189</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0.2658061837926173</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0.2290509122866451</v>
+      </c>
+      <c r="Q408" t="n">
         <v>20.26238212970023</v>
       </c>
     </row>
@@ -20056,6 +23856,18 @@
         <v>37.47487286057129</v>
       </c>
       <c r="M409" t="n">
+        <v>0.5692916832570974</v>
+      </c>
+      <c r="N409" t="n">
+        <v>0.4213991084751916</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0.9670266402430889</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0.4194122675986177</v>
+      </c>
+      <c r="Q409" t="n">
         <v>37.47487286057129</v>
       </c>
     </row>
@@ -20109,6 +23921,18 @@
         <v>27.73959329421981</v>
       </c>
       <c r="M410" t="n">
+        <v>1.202409887559015</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0.9407783635136241</v>
+      </c>
+      <c r="O410" t="n">
+        <v>2.359303174776628</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0.8758964970091244</v>
+      </c>
+      <c r="Q410" t="n">
         <v>27.73959329421981</v>
       </c>
     </row>
@@ -20162,6 +23986,18 @@
         <v>47.22703538814871</v>
       </c>
       <c r="M411" t="n">
+        <v>0.535795542893245</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0.5831285581799368</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0.8759849360785115</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0.4978104478567086</v>
+      </c>
+      <c r="Q411" t="n">
         <v>47.22703538814871</v>
       </c>
     </row>
@@ -20215,6 +24051,18 @@
         <v>36.60371721754899</v>
       </c>
       <c r="M412" t="n">
+        <v>0.4511433424228692</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0.4358786543897112</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0.9819333764781667</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0.4200079128978831</v>
+      </c>
+      <c r="Q412" t="n">
         <v>36.60371721754899</v>
       </c>
     </row>
@@ -20268,6 +24116,18 @@
         <v>16.17836560498422</v>
       </c>
       <c r="M413" t="n">
+        <v>1.609807902275451</v>
+      </c>
+      <c r="N413" t="n">
+        <v>0.5661287084492185</v>
+      </c>
+      <c r="O413" t="n">
+        <v>2.728714970904419</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0.5614536142395766</v>
+      </c>
+      <c r="Q413" t="n">
         <v>16.17836560498422</v>
       </c>
     </row>
@@ -20321,6 +24181,18 @@
         <v>30.23733705122546</v>
       </c>
       <c r="M414" t="n">
+        <v>0.5558672950891048</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0.3869829215954184</v>
+      </c>
+      <c r="O414" t="n">
+        <v>1.115859851997673</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0.2832744684786574</v>
+      </c>
+      <c r="Q414" t="n">
         <v>30.23733705122546</v>
       </c>
     </row>
@@ -20374,6 +24246,18 @@
         <v>15.46545886087575</v>
       </c>
       <c r="M415" t="n">
+        <v>0.9712118796422505</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0.7979704533818883</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0.8106906336517207</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0.5142209792077338</v>
+      </c>
+      <c r="Q415" t="n">
         <v>15.46545886087575</v>
       </c>
     </row>
@@ -20427,6 +24311,18 @@
         <v>29.36854044931852</v>
       </c>
       <c r="M416" t="n">
+        <v>0.2643576789827479</v>
+      </c>
+      <c r="N416" t="n">
+        <v>0.4114007374586487</v>
+      </c>
+      <c r="O416" t="n">
+        <v>0.2869138569215877</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0.246832885653633</v>
+      </c>
+      <c r="Q416" t="n">
         <v>29.36854044931852</v>
       </c>
     </row>
@@ -20480,6 +24376,18 @@
         <v>20.50673394496928</v>
       </c>
       <c r="M417" t="n">
+        <v>3.956909449474606</v>
+      </c>
+      <c r="N417" t="n">
+        <v>1.924597320809387</v>
+      </c>
+      <c r="O417" t="n">
+        <v>2.603392419091609</v>
+      </c>
+      <c r="P417" t="n">
+        <v>1.239252877443899</v>
+      </c>
+      <c r="Q417" t="n">
         <v>20.50673394496928</v>
       </c>
     </row>
@@ -20533,6 +24441,18 @@
         <v>32.5512775602791</v>
       </c>
       <c r="M418" t="n">
+        <v>0.5731794394337071</v>
+      </c>
+      <c r="N418" t="n">
+        <v>0.533677552331367</v>
+      </c>
+      <c r="O418" t="n">
+        <v>1.086588004348266</v>
+      </c>
+      <c r="P418" t="n">
+        <v>0.3557519816102508</v>
+      </c>
+      <c r="Q418" t="n">
         <v>32.5512775602791</v>
       </c>
     </row>
@@ -20586,6 +24506,18 @@
         <v>69.17437117858803</v>
       </c>
       <c r="M419" t="n">
+        <v>0.440099434869836</v>
+      </c>
+      <c r="N419" t="n">
+        <v>0.6446825089062704</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0.4234846262149743</v>
+      </c>
+      <c r="P419" t="n">
+        <v>0.4182369402250574</v>
+      </c>
+      <c r="Q419" t="n">
         <v>69.17437117858803</v>
       </c>
     </row>
@@ -20639,6 +24571,18 @@
         <v>78.70123331730203</v>
       </c>
       <c r="M420" t="n">
+        <v>1.058009486340628</v>
+      </c>
+      <c r="N420" t="n">
+        <v>1.340496888566604</v>
+      </c>
+      <c r="O420" t="n">
+        <v>1.254532602766554</v>
+      </c>
+      <c r="P420" t="n">
+        <v>1.028596229270688</v>
+      </c>
+      <c r="Q420" t="n">
         <v>78.70123331730203</v>
       </c>
     </row>
@@ -20692,6 +24636,18 @@
         <v>41.61930931151637</v>
       </c>
       <c r="M421" t="n">
+        <v>0.2498529350767176</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0.2795078392924772</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0.5620868415559113</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0.2359259979965313</v>
+      </c>
+      <c r="Q421" t="n">
         <v>41.61930931151637</v>
       </c>
     </row>
@@ -20745,6 +24701,18 @@
         <v>61.42607720534875</v>
       </c>
       <c r="M422" t="n">
+        <v>0.1485594887907052</v>
+      </c>
+      <c r="N422" t="n">
+        <v>0.1649397538041932</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0.2781837770363583</v>
+      </c>
+      <c r="P422" t="n">
+        <v>0.1696188786963956</v>
+      </c>
+      <c r="Q422" t="n">
         <v>61.42607720534875</v>
       </c>
     </row>
@@ -20798,6 +24766,18 @@
         <v>73.30260827474994</v>
       </c>
       <c r="M423" t="n">
+        <v>0.5670719646074951</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0.9115369574227635</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0.6732368938550292</v>
+      </c>
+      <c r="P423" t="n">
+        <v>0.5774017958397273</v>
+      </c>
+      <c r="Q423" t="n">
         <v>73.30260827474994</v>
       </c>
     </row>
@@ -20851,6 +24831,18 @@
         <v>88.11179310593992</v>
       </c>
       <c r="M424" t="n">
+        <v>0.5697785436893239</v>
+      </c>
+      <c r="N424" t="n">
+        <v>0.7703904390533843</v>
+      </c>
+      <c r="O424" t="n">
+        <v>0.5142167300938189</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0.5106190004402678</v>
+      </c>
+      <c r="Q424" t="n">
         <v>88.11179310593992</v>
       </c>
     </row>
@@ -20904,6 +24896,18 @@
         <v>68.38202998760241</v>
       </c>
       <c r="M425" t="n">
+        <v>0.5015906787487314</v>
+      </c>
+      <c r="N425" t="n">
+        <v>0.5038355355338973</v>
+      </c>
+      <c r="O425" t="n">
+        <v>0.5284984633870213</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0.4594891427006692</v>
+      </c>
+      <c r="Q425" t="n">
         <v>68.38202998760241</v>
       </c>
     </row>
@@ -20957,6 +24961,18 @@
         <v>33.17999504829733</v>
       </c>
       <c r="M426" t="n">
+        <v>0.6639147302699833</v>
+      </c>
+      <c r="N426" t="n">
+        <v>0.6487601633603632</v>
+      </c>
+      <c r="O426" t="n">
+        <v>1.689066163626003</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0.6461082194709546</v>
+      </c>
+      <c r="Q426" t="n">
         <v>33.17999504829733</v>
       </c>
     </row>
@@ -21010,6 +25026,18 @@
         <v>53.31734177396381</v>
       </c>
       <c r="M427" t="n">
+        <v>0.415101859044137</v>
+      </c>
+      <c r="N427" t="n">
+        <v>0.4614018939737696</v>
+      </c>
+      <c r="O427" t="n">
+        <v>0.7287376636808569</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0.4086738759083235</v>
+      </c>
+      <c r="Q427" t="n">
         <v>53.31734177396381</v>
       </c>
     </row>
@@ -21063,6 +25091,18 @@
         <v>52.9842309541708</v>
       </c>
       <c r="M428" t="n">
+        <v>0.2014113229745548</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0.2916285518069181</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0.3383528708811239</v>
+      </c>
+      <c r="P428" t="n">
+        <v>0.1890144924457634</v>
+      </c>
+      <c r="Q428" t="n">
         <v>52.9842309541708</v>
       </c>
     </row>
@@ -21116,6 +25156,18 @@
         <v>22.08903264948488</v>
       </c>
       <c r="M429" t="n">
+        <v>0.2853971868186587</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0.4998416327950066</v>
+      </c>
+      <c r="O429" t="n">
+        <v>1.137916061134378</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0.2540556462875793</v>
+      </c>
+      <c r="Q429" t="n">
         <v>22.08903264948488</v>
       </c>
     </row>
@@ -21169,6 +25221,18 @@
         <v>66.00743123213209</v>
       </c>
       <c r="M430" t="n">
+        <v>0.1609720253585035</v>
+      </c>
+      <c r="N430" t="n">
+        <v>0.1920896620430298</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0.2246663172331909</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0.16393159488648</v>
+      </c>
+      <c r="Q430" t="n">
         <v>66.00743123213209</v>
       </c>
     </row>
@@ -21222,6 +25286,18 @@
         <v>27.74939810816661</v>
       </c>
       <c r="M431" t="n">
+        <v>0.1951991729654962</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0.2673813346010064</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0.6285477015663237</v>
+      </c>
+      <c r="P431" t="n">
+        <v>0.2049681720166547</v>
+      </c>
+      <c r="Q431" t="n">
         <v>27.74939810816661</v>
       </c>
     </row>
@@ -21275,6 +25351,18 @@
         <v>44.7202366621401</v>
       </c>
       <c r="M432" t="n">
+        <v>0.2309026680644236</v>
+      </c>
+      <c r="N432" t="n">
+        <v>0.2411861338313643</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0.5116730356300899</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0.2359851972055219</v>
+      </c>
+      <c r="Q432" t="n">
         <v>44.7202366621401</v>
       </c>
     </row>
@@ -21328,6 +25416,18 @@
         <v>67.85897623014705</v>
       </c>
       <c r="M433" t="n">
+        <v>0.7839344441332532</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0.7067529350359539</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0.9494610790483037</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0.6719192584772705</v>
+      </c>
+      <c r="Q433" t="n">
         <v>67.85897623014705</v>
       </c>
     </row>
@@ -21381,6 +25481,18 @@
         <v>19.21638194006343</v>
       </c>
       <c r="M434" t="n">
+        <v>0.5687628404695694</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0.5654672986402896</v>
+      </c>
+      <c r="O434" t="n">
+        <v>1.885373593839309</v>
+      </c>
+      <c r="P434" t="n">
+        <v>0.4280840107668817</v>
+      </c>
+      <c r="Q434" t="n">
         <v>19.21638194006343</v>
       </c>
     </row>
@@ -21434,6 +25546,18 @@
         <v>44.79368247962142</v>
       </c>
       <c r="M435" t="n">
+        <v>0.3961822544872344</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0.531649088729069</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0.7221641065127123</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0.3958497038434048</v>
+      </c>
+      <c r="Q435" t="n">
         <v>44.79368247962142</v>
       </c>
     </row>
@@ -21487,6 +25611,18 @@
         <v>69.16177468694542</v>
       </c>
       <c r="M436" t="n">
+        <v>0.3760783401574072</v>
+      </c>
+      <c r="N436" t="n">
+        <v>0.4727660447062873</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0.4460509245054823</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0.362587421740165</v>
+      </c>
+      <c r="Q436" t="n">
         <v>69.16177468694542</v>
       </c>
     </row>
